--- a/data/trending_integrated_20260916_13.xlsx
+++ b/data/trending_integrated_20260916_13.xlsx
@@ -584,7 +584,7 @@
         <v>149</v>
       </c>
       <c r="G2" t="n">
-        <v>1080</v>
+        <v>1085</v>
       </c>
       <c r="H2" t="n">
         <v>1.03</v>
@@ -610,7 +610,7 @@
         <v>2.24</v>
       </c>
       <c r="O2" t="n">
-        <v>7420533570</v>
+        <v>7428140610</v>
       </c>
       <c r="P2" t="n">
         <v>6900</v>
@@ -670,13 +670,13 @@
         <v>-0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F3" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G3" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H3" t="n">
         <v>0.4</v>
@@ -702,7 +702,7 @@
         <v>0.42</v>
       </c>
       <c r="O3" t="n">
-        <v>172072008830</v>
+        <v>173161718580</v>
       </c>
       <c r="P3" t="n">
         <v>25700</v>
@@ -711,14 +711,14 @@
         <v>4600</v>
       </c>
       <c r="R3" t="n">
-        <v>23000</v>
+        <v>21000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>6G 통신 대장주 언급. 역대급 거래량 발생 및 상한가 기대감 표현. 실적 부재 및 개잡주 비판 의견 존재.</t>
+          <t>6G 통신 테마주 언급. 거래량 증가 및 급등 가능성 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['6G', '통신', '거래량']</t>
+          <t>['6G 통신', '거래량', '급등']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15900</v>
+        <v>15990</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+12.45%</t>
+          <t>'+13.08%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.15</v>
       </c>
       <c r="E4" t="n">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="F4" t="n">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="G4" t="n">
-        <v>1576</v>
+        <v>1628</v>
       </c>
       <c r="H4" t="n">
         <v>1.95</v>
@@ -794,7 +794,7 @@
         <v>1.8</v>
       </c>
       <c r="O4" t="n">
-        <v>546154960675</v>
+        <v>561158950570</v>
       </c>
       <c r="P4" t="n">
         <v>31500</v>
@@ -803,23 +803,23 @@
         <v>1272</v>
       </c>
       <c r="R4" t="n">
-        <v>574000</v>
+        <v>1050000</v>
       </c>
       <c r="S4" t="n">
-        <v>18000</v>
+        <v>41000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>외국인/기관 대량 순매수 및 미국 자회사 수주 발표에 따른 급등 기대. 10만원 목표가 언급.</t>
+          <t>미국 자회사 인캡의 대규모 광통신 수주 기대감 및 외국인/기관 대량 순매수 확인. 10만원 목표가 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['수주', '외국인']</t>
+          <t>['광통신', '수주', '대량 매수']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>씨피시스템</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4915</v>
+        <v>4405</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+9.22%</t>
+          <t>'+6.92%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.82</v>
+        <v>-0.03</v>
       </c>
       <c r="E5" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="F5" t="n">
-        <v>46</v>
+        <v>93</v>
       </c>
       <c r="G5" t="n">
-        <v>128</v>
+        <v>194</v>
       </c>
       <c r="H5" t="n">
-        <v>1.66</v>
+        <v>0.74</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>4500</v>
+        <v>4120</v>
       </c>
       <c r="K5" t="n">
-        <v>4480</v>
+        <v>4120</v>
       </c>
       <c r="L5" t="n">
-        <v>5400</v>
+        <v>4800</v>
       </c>
       <c r="M5" t="n">
-        <v>4290</v>
+        <v>4100</v>
       </c>
       <c r="N5" t="n">
-        <v>0.84</v>
+        <v>0.77</v>
       </c>
       <c r="O5" t="n">
-        <v>116365715424</v>
+        <v>304953790863</v>
       </c>
       <c r="P5" t="n">
-        <v>6190</v>
+        <v>8100</v>
       </c>
       <c r="Q5" t="n">
-        <v>1938</v>
+        <v>592</v>
       </c>
       <c r="R5" t="n">
-        <v>-121000</v>
+        <v>-119000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>10000원 직행 버스 언급하며 매수 독려. 시장 변동성 없을 때 대장주 역할 기대. 솔루션 공급 계약금액 공시 시 급등 전망.</t>
+          <t>광케이블 관련 긍정적 언급과 함께 '운전' 능숙함 언급. 상한가 및 10% 이상 상승 예상.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['대장주', '매수', '공시']</t>
+          <t>['광케이블', '상한가', '상승 예상']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>413630</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>씨피시스템</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4415</v>
+        <v>4785</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.16%</t>
+          <t>'+6.33%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.03</v>
+        <v>0.82</v>
       </c>
       <c r="E6" t="n">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="F6" t="n">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="G6" t="n">
-        <v>181</v>
+        <v>132</v>
       </c>
       <c r="H6" t="n">
-        <v>0.74</v>
+        <v>1.66</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>4120</v>
+        <v>4500</v>
       </c>
       <c r="K6" t="n">
-        <v>4120</v>
+        <v>4480</v>
       </c>
       <c r="L6" t="n">
-        <v>4800</v>
+        <v>5400</v>
       </c>
       <c r="M6" t="n">
-        <v>4100</v>
+        <v>4290</v>
       </c>
       <c r="N6" t="n">
-        <v>0.77</v>
+        <v>0.84</v>
       </c>
       <c r="O6" t="n">
-        <v>301438907021</v>
+        <v>119405187117</v>
       </c>
       <c r="P6" t="n">
-        <v>8100</v>
+        <v>6190</v>
       </c>
       <c r="Q6" t="n">
-        <v>592</v>
+        <v>1938</v>
       </c>
       <c r="R6" t="n">
-        <v>32000</v>
+        <v>-310000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>상승 추세 및 4천원 지지선 언급. 광케이블 관련주 상승 소식과 함께 상한가 기대감 표현. 적자 지속 리스크 존재.</t>
+          <t>삼성과의 4381억 공급 계약 체결 공시 확인. 주포 개입 및 단기 급등 가능성 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['추세', '광케이블', '적자']</t>
+          <t>['공급 계약', '주포', '단기 급등']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,86 +1016,86 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>413630</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3670</v>
+        <v>194500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.41%</t>
+          <t>'+3.96%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>121</v>
+        <v>53</v>
       </c>
       <c r="F7" t="n">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="G7" t="n">
-        <v>439</v>
+        <v>273</v>
       </c>
       <c r="H7" t="n">
-        <v>3.11</v>
+        <v>75.66</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3515</v>
+        <v>187100</v>
       </c>
       <c r="K7" t="n">
-        <v>4120</v>
+        <v>187200</v>
       </c>
       <c r="L7" t="n">
-        <v>4140</v>
+        <v>195900</v>
       </c>
       <c r="M7" t="n">
-        <v>3650</v>
+        <v>186100</v>
       </c>
       <c r="N7" t="n">
-        <v>3.16</v>
+        <v>75.67</v>
       </c>
       <c r="O7" t="n">
-        <v>16711998403</v>
+        <v>464009834150</v>
       </c>
       <c r="P7" t="n">
-        <v>16110</v>
+        <v>243500</v>
       </c>
       <c r="Q7" t="n">
-        <v>2300</v>
+        <v>61800</v>
       </c>
       <c r="R7" t="n">
-        <v>-335000</v>
+        <v>-216000</v>
       </c>
       <c r="S7" t="n">
-        <v>-158000</v>
+        <v>33000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>유한양행 최대주주 언급. 사기 도박판 및 나락간다 경고. 25-26년 적자 지속으로 인한 상폐 우려 제기.</t>
+          <t>우선주 매입 소각 및 배당 관련 긍정적 기대감, 본주와의 괴리율 축소 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['상폐', '적자', '공매도']</t>
+          <t>['우선주', '배당', '괴리율']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,82 +1103,82 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>424870</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>193700</v>
+        <v>7160</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.53%</t>
+          <t>'+3.77%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.01</v>
+        <v>0.09</v>
       </c>
       <c r="E8" t="n">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F8" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G8" t="n">
-        <v>266</v>
+        <v>60</v>
       </c>
       <c r="H8" t="n">
-        <v>75.66</v>
+        <v>0.79</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>187100</v>
+        <v>6900</v>
       </c>
       <c r="K8" t="n">
-        <v>187200</v>
+        <v>6770</v>
       </c>
       <c r="L8" t="n">
-        <v>195900</v>
+        <v>8590</v>
       </c>
       <c r="M8" t="n">
-        <v>186100</v>
+        <v>6660</v>
       </c>
       <c r="N8" t="n">
-        <v>75.67</v>
+        <v>0.7</v>
       </c>
       <c r="O8" t="n">
-        <v>448420670750</v>
+        <v>75791146320</v>
       </c>
       <c r="P8" t="n">
-        <v>243500</v>
+        <v>10360</v>
       </c>
       <c r="Q8" t="n">
-        <v>61800</v>
+        <v>2965</v>
       </c>
       <c r="R8" t="n">
-        <v>21000</v>
+        <v>74000</v>
       </c>
       <c r="S8" t="n">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>우선주 매입 소각 및 배당 관련 긍정적 기대감, 본주와의 괴리율 축소 전망.</t>
+          <t>보안 대장주로서의 지위 강조 및 AI 관련 논의 언급. 긍정적 흐름 기대.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['우선주', '배당', '괴리율']</t>
+          <t>['보안주', 'AI', '대장주']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7110</v>
+        <v>3637</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.04%</t>
+          <t>'+3.47%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.09</v>
+        <v>-0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="F9" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="G9" t="n">
-        <v>61</v>
+        <v>469</v>
       </c>
       <c r="H9" t="n">
-        <v>0.79</v>
+        <v>3.11</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,60 +1239,60 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>6900</v>
+        <v>3515</v>
       </c>
       <c r="K9" t="n">
-        <v>6770</v>
+        <v>4120</v>
       </c>
       <c r="L9" t="n">
-        <v>8590</v>
+        <v>4140</v>
       </c>
       <c r="M9" t="n">
-        <v>6660</v>
+        <v>3620</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7</v>
+        <v>3.16</v>
       </c>
       <c r="O9" t="n">
-        <v>75469340935</v>
+        <v>16966470462</v>
       </c>
       <c r="P9" t="n">
-        <v>10360</v>
+        <v>16110</v>
       </c>
       <c r="Q9" t="n">
-        <v>2965</v>
+        <v>2300</v>
       </c>
       <c r="R9" t="n">
-        <v>87000</v>
+        <v>-386000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-206000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>보안 대장주로서의 지위 강조 및 AI 관련 논의 언급. 긍정적 흐름 기대.</t>
+          <t>유한양행 자회사 언급. 재탕 뉴스 및 공매도 관련 부정적 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['보안주', 'AI', '대장주']</t>
+          <t>['유한양행', '재탕 뉴스', '공매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>424870</t>
         </is>
       </c>
     </row>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1739500</v>
+        <v>1746000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.93%</t>
+          <t>'+3.31%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="G10" t="n">
-        <v>1895</v>
+        <v>1926</v>
       </c>
       <c r="H10" t="n">
         <v>50.2</v>
@@ -1337,7 +1337,7 @@
         <v>1686000</v>
       </c>
       <c r="L10" t="n">
-        <v>1740000</v>
+        <v>1746000</v>
       </c>
       <c r="M10" t="n">
         <v>1686000</v>
@@ -1346,7 +1346,7 @@
         <v>50.27</v>
       </c>
       <c r="O10" t="n">
-        <v>2673491226500</v>
+        <v>2796663065000</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1355,23 +1355,23 @@
         <v>331500</v>
       </c>
       <c r="R10" t="n">
-        <v>-12000</v>
+        <v>-46000</v>
       </c>
       <c r="S10" t="n">
-        <v>40000</v>
+        <v>113000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>젠슨황 언급 및 외인 선물 매수 포착. 자사주 매입 및 소각 기대감과 함께 240만원 목표 주가 제시. 반도체 실적 시즌 언급.</t>
+          <t>외인 선물 매수와 함께 자사주 매입 및 소각 기대감 언급. 240만원 목표가 제시.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['젠슨황', '자사주매입', '반도체']</t>
+          <t>['자사주 매입', '자사주 소각', '외국인']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3455</v>
+        <v>3465</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.83%</t>
+          <t>'+3.12%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>85</v>
       </c>
       <c r="F11" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G11" t="n">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1438,7 +1438,7 @@
         <v>1.34</v>
       </c>
       <c r="O11" t="n">
-        <v>98763857553</v>
+        <v>99210477065</v>
       </c>
       <c r="P11" t="n">
         <v>5100</v>
@@ -1447,23 +1447,23 @@
         <v>966</v>
       </c>
       <c r="R11" t="n">
-        <v>9000</v>
+        <v>-31000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>양자암호 관련주로 부각, 트럼프 행정명령 및 미국 광통신 보안주 상승 영향 언급. 삼성과 4381억 공급 계약 체결 사실 확인.</t>
+          <t>양자내성암호 독점 공급 및 미국 광통신 보안주 상승 이슈에 기반한 기대감. 양자보안 대장주 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['양자암호', '공급계약', '보안주']</t>
+          <t>['양자내성암호', '보안주', '독점 공급']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13610</v>
+        <v>13580</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.33%</t>
+          <t>'+2.11%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F12" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G12" t="n">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>13767896570</v>
+        <v>15356048235</v>
       </c>
       <c r="P12" t="n">
         <v>19380</v>
@@ -1539,10 +1539,10 @@
         <v>3200</v>
       </c>
       <c r="R12" t="n">
-        <v>-22000</v>
+        <v>-1000</v>
       </c>
       <c r="S12" t="n">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>253250</v>
+        <v>253500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+1.91%</t>
+          <t>'+2.01%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="G13" t="n">
-        <v>1437</v>
+        <v>1419</v>
       </c>
       <c r="H13" t="n">
         <v>46.56</v>
@@ -1613,7 +1613,7 @@
         <v>248000</v>
       </c>
       <c r="L13" t="n">
-        <v>253500</v>
+        <v>254000</v>
       </c>
       <c r="M13" t="n">
         <v>247500</v>
@@ -1622,7 +1622,7 @@
         <v>46.57</v>
       </c>
       <c r="O13" t="n">
-        <v>1626995550750</v>
+        <v>1695795460750</v>
       </c>
       <c r="P13" t="n">
         <v>374500</v>
@@ -1631,14 +1631,14 @@
         <v>76700</v>
       </c>
       <c r="R13" t="n">
-        <v>-573000</v>
+        <v>-720000</v>
       </c>
       <c r="S13" t="n">
-        <v>259000</v>
+        <v>754000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>3분기 배당금 및 연말 최고점 돌파 기대감 언급. 정치적 이슈와 함께 국내 증시 하락에 대한 부정적 의견 존재.</t>
+          <t>배당금 및 연말 최고점 돌파 기대감과 함께 정치적 이슈, 국민연금, 이재명 관련 부정적 언급 다수.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['배당금', '최고점', '증시']</t>
+          <t>['배당금', '정치', '국민연금']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10180</v>
+        <v>10090</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.59%</t>
+          <t>'-0.30%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F14" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G14" t="n">
-        <v>258</v>
+        <v>281</v>
       </c>
       <c r="H14" t="n">
         <v>0.67</v>
@@ -1714,7 +1714,7 @@
         <v>0.6</v>
       </c>
       <c r="O14" t="n">
-        <v>112531939690</v>
+        <v>113903349500</v>
       </c>
       <c r="P14" t="n">
         <v>15960</v>
@@ -1723,23 +1723,23 @@
         <v>3500</v>
       </c>
       <c r="R14" t="n">
-        <v>-9000</v>
+        <v>-59000</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미프진 독점 공급 재료로 인한 단기 주가 상승 기대. 도입 시점 불확실성 존재.</t>
+          <t>미프진 관련 현대약품의 독점 공급 이슈가 있으나, 도입 시점 및 재료 소멸에 대한 상반된 의견이 존재.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['미프진', '독점공급']</t>
+          <t>['미프진', '독점 공급', '재료 소멸']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8530</v>
+        <v>8520</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-0.93%</t>
+          <t>'-1.05%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.5</v>
       </c>
       <c r="E15" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F15" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G15" t="n">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="H15" t="n">
         <v>26.66</v>
@@ -1806,7 +1806,7 @@
         <v>27.16</v>
       </c>
       <c r="O15" t="n">
-        <v>10615317650</v>
+        <v>10699334005</v>
       </c>
       <c r="P15" t="n">
         <v>17950</v>
@@ -1815,23 +1815,23 @@
         <v>8120</v>
       </c>
       <c r="R15" t="n">
-        <v>-528000</v>
+        <v>-492000</v>
       </c>
       <c r="S15" t="n">
-        <v>-36000</v>
+        <v>-58000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>삼성디스플레이와 비교되며 저평가 논란. 경영진 성과급 및 부채 문제 언급.</t>
+          <t>삼성디스플레이와의 비교 언급 및 FLiPP 양산 기대감 있으나, 재무 상태, 외인 매도세, 경영진 관련 부정적 의견 다수.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['PBR', '삼성디스플레이']</t>
+          <t>['FLiPP', '재무', '외인 매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18840</v>
+        <v>18810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.52%</t>
+          <t>'-1.67%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.11</v>
       </c>
       <c r="E16" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F16" t="n">
         <v>61</v>
       </c>
       <c r="G16" t="n">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="H16" t="n">
         <v>10.64</v>
@@ -1898,7 +1898,7 @@
         <v>10.53</v>
       </c>
       <c r="O16" t="n">
-        <v>46387686645</v>
+        <v>48456720580</v>
       </c>
       <c r="P16" t="n">
         <v>40350</v>
@@ -1907,14 +1907,14 @@
         <v>3320</v>
       </c>
       <c r="R16" t="n">
-        <v>-204000</v>
+        <v>-116000</v>
       </c>
       <c r="S16" t="n">
-        <v>-37000</v>
+        <v>-90000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>주가 조작 의혹과 함께 대차 해지 운동 동참 독려. 대형 계약 임박 및 10만원 이상 주가 상승 전망.</t>
+          <t>대차해지 운동 독려와 함께 주가조작 의혹 제기. 대형 계약 임박 및 10만원 이상 목표가 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['주가조작', '대차해지', '대형계약']</t>
+          <t>['대차해지', '주가조작', '대형 계약']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20350</v>
+        <v>20300</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.69%</t>
+          <t>'-1.93%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.39</v>
       </c>
       <c r="E17" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F17" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G17" t="n">
-        <v>272</v>
+        <v>295</v>
       </c>
       <c r="H17" t="n">
         <v>28.51</v>
@@ -1990,7 +1990,7 @@
         <v>28.9</v>
       </c>
       <c r="O17" t="n">
-        <v>22578734500</v>
+        <v>23649388775</v>
       </c>
       <c r="P17" t="n">
         <v>35350</v>
@@ -1999,23 +1999,23 @@
         <v>18440</v>
       </c>
       <c r="R17" t="n">
-        <v>-332000</v>
+        <v>-677000</v>
       </c>
       <c r="S17" t="n">
-        <v>-18000</v>
+        <v>-51000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>IBK투자증권의 목표주가 3만7000원 및 매수 의견 제시. 1.6조 LNG선 수주 소식에도 불구하고 주가 하락 및 공매도에 대한 불만 표출.</t>
+          <t>LNG선 수주 및 IBK 목표주가 상향 언급에도 불구하고, 매도 타이밍, 쓰레기 주식 등 부정적 의견 지배적.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['LNG선', '수주', '공매도']</t>
+          <t>['LNG선', '수주', '목표주가']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2035,83 +2035,83 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>한컴위드</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5120</v>
+        <v>10440</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.10%</t>
+          <t>'-2.06%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-1.39</v>
+        <v>1.29</v>
       </c>
       <c r="E18" t="n">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="F18" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="G18" t="n">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="H18" t="n">
-        <v>1.29</v>
+        <v>19.22</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>5230</v>
+        <v>10660</v>
       </c>
       <c r="K18" t="n">
-        <v>5750</v>
+        <v>10500</v>
       </c>
       <c r="L18" t="n">
-        <v>5880</v>
+        <v>10900</v>
       </c>
       <c r="M18" t="n">
-        <v>5020</v>
+        <v>10060</v>
       </c>
       <c r="N18" t="n">
-        <v>2.68</v>
+        <v>17.93</v>
       </c>
       <c r="O18" t="n">
-        <v>61651829600</v>
+        <v>115356178985</v>
       </c>
       <c r="P18" t="n">
-        <v>8980</v>
+        <v>22450</v>
       </c>
       <c r="Q18" t="n">
-        <v>2795</v>
+        <v>1760</v>
       </c>
       <c r="R18" t="n">
-        <v>308000</v>
+        <v>-475000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>양자보안 관련주로 부각, 미 보안주 상승 및 11월 양자보안 구축 의무화 관련 내용 언급. 삼성과 4381억 계약 체결 호재.</t>
+          <t>300만주 흡수 후 급등 가능성 언급. 기타법인 매도 및 투자주의 해제 예정.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['양자보안', '공급계약', '보안주']</t>
+          <t>['거래량', '투자주의']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>054920</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10415</v>
+        <v>84200</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.30%</t>
+          <t>'-2.32%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1.29</v>
+        <v>-0.08</v>
       </c>
       <c r="E19" t="n">
-        <v>99</v>
+        <v>266</v>
       </c>
       <c r="F19" t="n">
-        <v>63</v>
+        <v>144</v>
       </c>
       <c r="G19" t="n">
-        <v>164</v>
+        <v>817</v>
       </c>
       <c r="H19" t="n">
-        <v>19.22</v>
+        <v>23.37</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,51 +2159,51 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>10660</v>
+        <v>86200</v>
       </c>
       <c r="K19" t="n">
-        <v>10500</v>
+        <v>86200</v>
       </c>
       <c r="L19" t="n">
-        <v>10900</v>
+        <v>86300</v>
       </c>
       <c r="M19" t="n">
-        <v>10060</v>
+        <v>83500</v>
       </c>
       <c r="N19" t="n">
-        <v>17.93</v>
+        <v>23.45</v>
       </c>
       <c r="O19" t="n">
-        <v>114217844025</v>
+        <v>121410895800</v>
       </c>
       <c r="P19" t="n">
-        <v>22450</v>
+        <v>139200</v>
       </c>
       <c r="Q19" t="n">
-        <v>1760</v>
+        <v>57000</v>
       </c>
       <c r="R19" t="n">
-        <v>-569000</v>
+        <v>-102000</v>
       </c>
       <c r="S19" t="n">
-        <v>1000</v>
+        <v>-86000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>300만주 흡수 후 급등 가능성 언급. 기타법인 매도 및 투자주의 해제 예정.</t>
+          <t>웨스팅하우스 지분 인수 이슈에 대한 기대감과 공매도 세력에 대한 부정적 언급 공존. 상반된 전망 제시.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['거래량', '투자주의']</t>
+          <t>['웨스팅하우스', '공매도', '지분 인수']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,90 +2212,90 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>84200</v>
+        <v>31550</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-2.32%</t>
+          <t>'-2.77%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.08</v>
+        <v>-0.34</v>
       </c>
       <c r="E20" t="n">
-        <v>258</v>
+        <v>205</v>
       </c>
       <c r="F20" t="n">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="G20" t="n">
-        <v>777</v>
+        <v>1116</v>
       </c>
       <c r="H20" t="n">
-        <v>23.37</v>
+        <v>17.16</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>86200</v>
+        <v>32450</v>
       </c>
       <c r="K20" t="n">
-        <v>86200</v>
+        <v>32850</v>
       </c>
       <c r="L20" t="n">
-        <v>86300</v>
+        <v>32850</v>
       </c>
       <c r="M20" t="n">
-        <v>83500</v>
+        <v>30900</v>
       </c>
       <c r="N20" t="n">
-        <v>23.45</v>
+        <v>17.5</v>
       </c>
       <c r="O20" t="n">
-        <v>119206098100</v>
+        <v>8549575200</v>
       </c>
       <c r="P20" t="n">
-        <v>139200</v>
+        <v>69200</v>
       </c>
       <c r="Q20" t="n">
-        <v>57000</v>
+        <v>24150</v>
       </c>
       <c r="R20" t="n">
-        <v>-137000</v>
+        <v>-83000</v>
       </c>
       <c r="S20" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>웨스팅하우스 지분 인수 관련 기대감 속 공매도 공방 및 단기 변동성 예상.</t>
+          <t>유럽 담관암 신약 신청 관련 불확실성 속 FDA 실패 가능성 제기. 과거 신약 실패 경험과 공모주 청약 시점의 유럽 신청에 대한 의구심이 공존.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['웨스팅하우스', '공매도', '지분인수']</t>
+          <t>['담관암', 'FDA', '신약 신청']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,38 +2304,38 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>한컴위드</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>31650</v>
+        <v>5080</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-2.47%</t>
+          <t>'-2.87%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.34</v>
+        <v>-1.39</v>
       </c>
       <c r="E21" t="n">
-        <v>207</v>
+        <v>85</v>
       </c>
       <c r="F21" t="n">
-        <v>131</v>
+        <v>50</v>
       </c>
       <c r="G21" t="n">
-        <v>1111</v>
+        <v>173</v>
       </c>
       <c r="H21" t="n">
-        <v>17.16</v>
+        <v>1.29</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,47 +2343,47 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>32450</v>
+        <v>5230</v>
       </c>
       <c r="K21" t="n">
-        <v>32850</v>
+        <v>5750</v>
       </c>
       <c r="L21" t="n">
-        <v>32850</v>
+        <v>5880</v>
       </c>
       <c r="M21" t="n">
-        <v>30900</v>
+        <v>5020</v>
       </c>
       <c r="N21" t="n">
-        <v>17.5</v>
+        <v>2.68</v>
       </c>
       <c r="O21" t="n">
-        <v>8457144050</v>
+        <v>62008715500</v>
       </c>
       <c r="P21" t="n">
-        <v>69200</v>
+        <v>8980</v>
       </c>
       <c r="Q21" t="n">
-        <v>24150</v>
+        <v>2795</v>
       </c>
       <c r="R21" t="n">
-        <v>-71000</v>
+        <v>98000</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>유럽 담관암 신약 신청 관련 불확실성 속 FDA 실패 가능성 제기. 과거 신약 실패 경험과 공모주 청약 시점의 유럽 신청에 대한 의구심이 공존.</t>
+          <t>미국 사이버 보안주 강세 및 양자 보안 관련 기술 분석. 허매수 및 급등 가능성 언급.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['담관암', 'FDA', '신약 신청']</t>
+          <t>['사이버 보안', '양자 보안', '기술 분석']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>054920</t>
         </is>
       </c>
     </row>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17010</v>
+        <v>17020</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-3.08%</t>
+          <t>'-3.02%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0.1</v>
       </c>
       <c r="E22" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F22" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G22" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H22" t="n">
         <v>0.45</v>
@@ -2450,7 +2450,7 @@
         <v>0.35</v>
       </c>
       <c r="O22" t="n">
-        <v>156862476725</v>
+        <v>157464774830</v>
       </c>
       <c r="P22" t="n">
         <v>30550</v>
@@ -2459,7 +2459,7 @@
         <v>6100</v>
       </c>
       <c r="R22" t="n">
-        <v>-60000</v>
+        <v>-14000</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2495,31 +2495,31 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13990</v>
+        <v>5890</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-6.61%</t>
+          <t>'-6.66%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>-2.04</v>
       </c>
       <c r="E23" t="n">
-        <v>232</v>
+        <v>93</v>
       </c>
       <c r="F23" t="n">
-        <v>121</v>
+        <v>53</v>
       </c>
       <c r="G23" t="n">
-        <v>541</v>
+        <v>174</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,51 +2527,51 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>14980</v>
+        <v>6310</v>
       </c>
       <c r="K23" t="n">
-        <v>15300</v>
+        <v>6390</v>
       </c>
       <c r="L23" t="n">
-        <v>15580</v>
+        <v>6450</v>
       </c>
       <c r="M23" t="n">
-        <v>13520</v>
+        <v>5630</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O23" t="n">
-        <v>32315276700</v>
+        <v>41444123125</v>
       </c>
       <c r="P23" t="n">
-        <v>36200</v>
+        <v>11370</v>
       </c>
       <c r="Q23" t="n">
-        <v>8920</v>
+        <v>3300</v>
       </c>
       <c r="R23" t="n">
-        <v>-11000</v>
+        <v>342000</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>국제유가 상승 및 중동 지역 긴장 고조에도 불구하고 주가 하락에 대한 의문.</t>
+          <t xml:space="preserve">미국 클래리티 법안 부결 소식에 따른 가상자산 관련주 관심 증폭. 공매도 거래량 및 외국인 순매수 데이터 혼재. 향후 주가 추세에 대한 엇갈린 전망.  </t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['국제유가', '에너지주', '급락']</t>
+          <t>['클래리티법', '공매도', '외국인']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,38 +2580,38 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5880</v>
+        <v>13950</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-6.81%</t>
+          <t>'-6.88%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-2.04</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>93</v>
+        <v>232</v>
       </c>
       <c r="F24" t="n">
-        <v>53</v>
+        <v>121</v>
       </c>
       <c r="G24" t="n">
-        <v>173</v>
+        <v>551</v>
       </c>
       <c r="H24" t="n">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2619,38 +2619,38 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>6310</v>
+        <v>14980</v>
       </c>
       <c r="K24" t="n">
-        <v>6390</v>
+        <v>15300</v>
       </c>
       <c r="L24" t="n">
-        <v>6450</v>
+        <v>15580</v>
       </c>
       <c r="M24" t="n">
-        <v>5630</v>
+        <v>13520</v>
       </c>
       <c r="N24" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>41083879460</v>
+        <v>32732347120</v>
       </c>
       <c r="P24" t="n">
-        <v>11370</v>
+        <v>36200</v>
       </c>
       <c r="Q24" t="n">
-        <v>3300</v>
+        <v>8920</v>
       </c>
       <c r="R24" t="n">
-        <v>389000</v>
+        <v>-2000</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t xml:space="preserve">미국 클래리티 법안 부결 소식에 따른 가상자산 관련주 관심 증폭. 공매도 거래량 및 외국인 순매수 데이터 혼재. 향후 주가 추세에 대한 엇갈린 전망.  </t>
+          <t>국제 유가 상승 및 미장 에너지주 폭등 관련 언급. 비축유 및 이란 관련 이슈로 급락 가능성 경고.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
@@ -2659,11 +2659,11 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['클래리티법', '공매도', '외국인']</t>
+          <t>['국제 유가', '비축유', '급락']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>024060</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260916_13.xlsx
+++ b/data/trending_integrated_20260916_13.xlsx
@@ -584,7 +584,7 @@
         <v>149</v>
       </c>
       <c r="G2" t="n">
-        <v>1085</v>
+        <v>1106</v>
       </c>
       <c r="H2" t="n">
         <v>1.03</v>
@@ -610,7 +610,7 @@
         <v>2.24</v>
       </c>
       <c r="O2" t="n">
-        <v>7428140610</v>
+        <v>7432065090</v>
       </c>
       <c r="P2" t="n">
         <v>6900</v>
@@ -659,21 +659,21 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13500</v>
+        <v>13540</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+26.17%</t>
+          <t>'+26.54%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F3" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G3" t="n">
         <v>95</v>
@@ -702,7 +702,7 @@
         <v>0.42</v>
       </c>
       <c r="O3" t="n">
-        <v>173161718580</v>
+        <v>173677679120</v>
       </c>
       <c r="P3" t="n">
         <v>25700</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15990</v>
+        <v>16100</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.08%</t>
+          <t>'+13.86%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.15</v>
       </c>
       <c r="E4" t="n">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="F4" t="n">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="G4" t="n">
-        <v>1628</v>
+        <v>1681</v>
       </c>
       <c r="H4" t="n">
         <v>1.95</v>
@@ -794,7 +794,7 @@
         <v>1.8</v>
       </c>
       <c r="O4" t="n">
-        <v>561158950570</v>
+        <v>569527308215</v>
       </c>
       <c r="P4" t="n">
         <v>31500</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 자회사 인캡의 대규모 광통신 수주 기대감 및 외국인/기관 대량 순매수 확인. 10만원 목표가 언급.</t>
+          <t>외국인/기관 600억 대량 순매수 및 미국 자회사 대규모 광통신 수주. 10만원 목표 주가 제시 및 우상향 추세 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['광통신', '수주', '대량 매수']</t>
+          <t>['외국인 순매수', '광통신 수주', '대장주']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,21 +843,21 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4405</v>
+        <v>4475</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.92%</t>
+          <t>'+8.62%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.03</v>
       </c>
       <c r="E5" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="F5" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="G5" t="n">
         <v>194</v>
@@ -886,7 +886,7 @@
         <v>0.77</v>
       </c>
       <c r="O5" t="n">
-        <v>304953790863</v>
+        <v>306940089441</v>
       </c>
       <c r="P5" t="n">
         <v>8100</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>광케이블 관련 긍정적 언급과 함께 '운전' 능숙함 언급. 상한가 및 10% 이상 상승 예상.</t>
+          <t>광통신 섹터 상승 모멘텀과 연계된 기대감. 4천원 지지선 확보 및 대량 거래량 발생 시 20% 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['광케이블', '상한가', '상승 예상']</t>
+          <t>['광통신', '거래량', '지지선']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4785</v>
+        <v>4730</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.33%</t>
+          <t>'+5.11%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.82</v>
       </c>
       <c r="E6" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F6" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G6" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="H6" t="n">
         <v>1.66</v>
@@ -978,7 +978,7 @@
         <v>0.84</v>
       </c>
       <c r="O6" t="n">
-        <v>119405187117</v>
+        <v>120327661721</v>
       </c>
       <c r="P6" t="n">
         <v>6190</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>삼성과의 4381억 공급 계약 체결 공시 확인. 주포 개입 및 단기 급등 가능성 언급.</t>
+          <t>삼성과 4381억 규모 공급 계약 체결 가능성 언급. 재료 기반 급등 기대감 및 주포의 단타 매매 의혹.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['공급 계약', '주포', '단기 급등']</t>
+          <t>['공급 계약', '주포', '재료']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>194500</v>
+        <v>194700</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+3.96%</t>
+          <t>'+4.06%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F7" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G7" t="n">
-        <v>273</v>
+        <v>301</v>
       </c>
       <c r="H7" t="n">
         <v>75.66</v>
@@ -1070,7 +1070,7 @@
         <v>75.67</v>
       </c>
       <c r="O7" t="n">
-        <v>464009834150</v>
+        <v>474082253200</v>
       </c>
       <c r="P7" t="n">
         <v>243500</v>
@@ -1115,123 +1115,123 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7160</v>
+        <v>1749000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.77%</t>
+          <t>'+3.49%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.09</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>69</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>38</v>
+        <v>472</v>
       </c>
       <c r="G8" t="n">
-        <v>60</v>
+        <v>1984</v>
       </c>
       <c r="H8" t="n">
-        <v>0.79</v>
+        <v>50.2</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>6900</v>
+        <v>1690000</v>
       </c>
       <c r="K8" t="n">
-        <v>6770</v>
+        <v>1686000</v>
       </c>
       <c r="L8" t="n">
-        <v>8590</v>
+        <v>1750000</v>
       </c>
       <c r="M8" t="n">
-        <v>6660</v>
+        <v>1686000</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7</v>
+        <v>50.27</v>
       </c>
       <c r="O8" t="n">
-        <v>75791146320</v>
+        <v>2909620347500</v>
       </c>
       <c r="P8" t="n">
-        <v>10360</v>
+        <v>2987000</v>
       </c>
       <c r="Q8" t="n">
-        <v>2965</v>
+        <v>331500</v>
       </c>
       <c r="R8" t="n">
-        <v>74000</v>
+        <v>-46000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>113000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>보안 대장주로서의 지위 강조 및 AI 관련 논의 언급. 긍정적 흐름 기대.</t>
+          <t>외인 선물 대량 매수 및 기관 자금 유입 기대감. 자사주 매입 및 소각 기대감으로 인한 상승 전망. 반도체 실적 발표 시즌.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['보안주', 'AI', '대장주']</t>
+          <t>['자사주 매입', '기관 매수', '반도체 실적']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>72</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3637</v>
+        <v>7140</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.47%</t>
+          <t>'+3.48%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.05</v>
+        <v>0.09</v>
       </c>
       <c r="E9" t="n">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="F9" t="n">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="G9" t="n">
-        <v>469</v>
+        <v>60</v>
       </c>
       <c r="H9" t="n">
-        <v>3.11</v>
+        <v>0.79</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,143 +1239,143 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>3515</v>
+        <v>6900</v>
       </c>
       <c r="K9" t="n">
-        <v>4120</v>
+        <v>6770</v>
       </c>
       <c r="L9" t="n">
-        <v>4140</v>
+        <v>8590</v>
       </c>
       <c r="M9" t="n">
-        <v>3620</v>
+        <v>6660</v>
       </c>
       <c r="N9" t="n">
-        <v>3.16</v>
+        <v>0.7</v>
       </c>
       <c r="O9" t="n">
-        <v>16966470462</v>
+        <v>75955624390</v>
       </c>
       <c r="P9" t="n">
-        <v>16110</v>
+        <v>10360</v>
       </c>
       <c r="Q9" t="n">
-        <v>2300</v>
+        <v>2965</v>
       </c>
       <c r="R9" t="n">
-        <v>-386000</v>
+        <v>74000</v>
       </c>
       <c r="S9" t="n">
-        <v>-206000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>유한양행 자회사 언급. 재탕 뉴스 및 공매도 관련 부정적 전망.</t>
+          <t>보안 대장주로서의 지위 강조 및 AI 관련 논의 언급. 긍정적 흐름 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['유한양행', '재탕 뉴스', '공매도']</t>
+          <t>['보안주', 'AI', '대장주']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>424870</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1746000</v>
+        <v>3620</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.31%</t>
+          <t>'+2.99%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>127</v>
       </c>
       <c r="F10" t="n">
-        <v>473</v>
+        <v>73</v>
       </c>
       <c r="G10" t="n">
-        <v>1926</v>
+        <v>486</v>
       </c>
       <c r="H10" t="n">
-        <v>50.2</v>
+        <v>3.11</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1690000</v>
+        <v>3515</v>
       </c>
       <c r="K10" t="n">
-        <v>1686000</v>
+        <v>4120</v>
       </c>
       <c r="L10" t="n">
-        <v>1746000</v>
+        <v>4140</v>
       </c>
       <c r="M10" t="n">
-        <v>1686000</v>
+        <v>3615</v>
       </c>
       <c r="N10" t="n">
-        <v>50.27</v>
+        <v>3.16</v>
       </c>
       <c r="O10" t="n">
-        <v>2796663065000</v>
+        <v>17200579208</v>
       </c>
       <c r="P10" t="n">
-        <v>2987000</v>
+        <v>16110</v>
       </c>
       <c r="Q10" t="n">
-        <v>331500</v>
+        <v>2300</v>
       </c>
       <c r="R10" t="n">
-        <v>-46000</v>
+        <v>-386000</v>
       </c>
       <c r="S10" t="n">
-        <v>113000</v>
+        <v>-206000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>외인 선물 매수와 함께 자사주 매입 및 소각 기대감 언급. 240만원 목표가 제시.</t>
+          <t>최대주주 유한양행 확인, 그러나 과거 급등 후 하락 및 재탕 뉴스에 대한 투자자 불신 심화.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['자사주 매입', '자사주 소각', '외국인']</t>
+          <t>['바이오', '공매도', '최대주주']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,77 +1384,77 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>424870</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>한국첨단소재</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3465</v>
+        <v>253500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+3.12%</t>
+          <t>'+2.01%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-1.34</v>
+        <v>-0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>85</v>
+        <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>55</v>
+        <v>452</v>
       </c>
       <c r="G11" t="n">
-        <v>181</v>
+        <v>1403</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>46.56</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>3360</v>
+        <v>248500</v>
       </c>
       <c r="K11" t="n">
-        <v>3570</v>
+        <v>248000</v>
       </c>
       <c r="L11" t="n">
-        <v>3910</v>
+        <v>254000</v>
       </c>
       <c r="M11" t="n">
-        <v>3345</v>
+        <v>247500</v>
       </c>
       <c r="N11" t="n">
-        <v>1.34</v>
+        <v>46.57</v>
       </c>
       <c r="O11" t="n">
-        <v>99210477065</v>
+        <v>1732789971250</v>
       </c>
       <c r="P11" t="n">
-        <v>5100</v>
+        <v>374500</v>
       </c>
       <c r="Q11" t="n">
-        <v>966</v>
+        <v>76700</v>
       </c>
       <c r="R11" t="n">
-        <v>-31000</v>
+        <v>-720000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>754000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>양자내성암호 독점 공급 및 미국 광통신 보안주 상승 이슈에 기반한 기대감. 양자보안 대장주 언급.</t>
+          <t>연말 최고점 돌파 기대감 속 정치적 이슈 및 시장 침체 우려 상존. 30조 배당 및 3분기 실적 호조 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['양자내성암호', '보안주', '독점 공급']</t>
+          <t>['반도체', '배당', '정치적 이슈']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>107</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>062970</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13580</v>
+        <v>13540</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.11%</t>
+          <t>'+1.80%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F12" t="n">
         <v>42</v>
       </c>
       <c r="G12" t="n">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>15356048235</v>
+        <v>15796939880</v>
       </c>
       <c r="P12" t="n">
         <v>19380</v>
@@ -1575,83 +1575,83 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>253500</v>
+        <v>3420</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.01%</t>
+          <t>'+1.79%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.01</v>
+        <v>-1.34</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>86</v>
       </c>
       <c r="F13" t="n">
-        <v>449</v>
+        <v>56</v>
       </c>
       <c r="G13" t="n">
-        <v>1419</v>
+        <v>185</v>
       </c>
       <c r="H13" t="n">
-        <v>46.56</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>248500</v>
+        <v>3360</v>
       </c>
       <c r="K13" t="n">
-        <v>248000</v>
+        <v>3570</v>
       </c>
       <c r="L13" t="n">
-        <v>254000</v>
+        <v>3910</v>
       </c>
       <c r="M13" t="n">
-        <v>247500</v>
+        <v>3345</v>
       </c>
       <c r="N13" t="n">
-        <v>46.57</v>
+        <v>1.34</v>
       </c>
       <c r="O13" t="n">
-        <v>1695795460750</v>
+        <v>99827480227</v>
       </c>
       <c r="P13" t="n">
-        <v>374500</v>
+        <v>5100</v>
       </c>
       <c r="Q13" t="n">
-        <v>76700</v>
+        <v>966</v>
       </c>
       <c r="R13" t="n">
-        <v>-720000</v>
+        <v>-31000</v>
       </c>
       <c r="S13" t="n">
-        <v>754000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>배당금 및 연말 최고점 돌파 기대감과 함께 정치적 이슈, 국민연금, 이재명 관련 부정적 언급 다수.</t>
+          <t>양자내성암호 행정명령 및 양자암호 해독키 독점 공급 기대감. 미국 광통신 보안주 상승 및 가벼운 주가 흐름.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['배당금', '정치', '국민연금']</t>
+          <t>['양자암호', '보안주', '독점 공급']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>107</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>062970</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10090</v>
+        <v>10150</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.30%</t>
+          <t>'+0.30%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F14" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G14" t="n">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="H14" t="n">
         <v>0.67</v>
@@ -1714,7 +1714,7 @@
         <v>0.6</v>
       </c>
       <c r="O14" t="n">
-        <v>113903349500</v>
+        <v>114536701885</v>
       </c>
       <c r="P14" t="n">
         <v>15960</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미프진 관련 현대약품의 독점 공급 이슈가 있으나, 도입 시점 및 재료 소멸에 대한 상반된 의견이 존재.</t>
+          <t>미프진 독점 공급 계약 및 내년 1분기 도입 소식 기반 기대감. 재료 소멸 논쟁 상존.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8520</v>
+        <v>8500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.05%</t>
+          <t>'-1.28%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.5</v>
       </c>
       <c r="E15" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F15" t="n">
         <v>57</v>
       </c>
       <c r="G15" t="n">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="H15" t="n">
         <v>26.66</v>
@@ -1806,7 +1806,7 @@
         <v>27.16</v>
       </c>
       <c r="O15" t="n">
-        <v>10699334005</v>
+        <v>10976419430</v>
       </c>
       <c r="P15" t="n">
         <v>17950</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18810</v>
+        <v>18780</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.67%</t>
+          <t>'-1.83%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.11</v>
       </c>
       <c r="E16" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F16" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G16" t="n">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="H16" t="n">
         <v>10.64</v>
@@ -1898,7 +1898,7 @@
         <v>10.53</v>
       </c>
       <c r="O16" t="n">
-        <v>48456720580</v>
+        <v>49382161465</v>
       </c>
       <c r="P16" t="n">
         <v>40350</v>
@@ -1943,31 +1943,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20300</v>
+        <v>10450</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.93%</t>
+          <t>'-1.97%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.39</v>
+        <v>1.29</v>
       </c>
       <c r="E17" t="n">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="F17" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G17" t="n">
-        <v>295</v>
+        <v>164</v>
       </c>
       <c r="H17" t="n">
-        <v>28.51</v>
+        <v>19.22</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,47 +1975,47 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>20700</v>
+        <v>10660</v>
       </c>
       <c r="K17" t="n">
-        <v>20750</v>
+        <v>10500</v>
       </c>
       <c r="L17" t="n">
-        <v>20750</v>
+        <v>10900</v>
       </c>
       <c r="M17" t="n">
-        <v>20250</v>
+        <v>10060</v>
       </c>
       <c r="N17" t="n">
-        <v>28.9</v>
+        <v>17.93</v>
       </c>
       <c r="O17" t="n">
-        <v>23649388775</v>
+        <v>115943796025</v>
       </c>
       <c r="P17" t="n">
-        <v>35350</v>
+        <v>22450</v>
       </c>
       <c r="Q17" t="n">
-        <v>18440</v>
+        <v>1760</v>
       </c>
       <c r="R17" t="n">
-        <v>-677000</v>
+        <v>-475000</v>
       </c>
       <c r="S17" t="n">
-        <v>-51000</v>
+        <v>2000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>LNG선 수주 및 IBK 목표주가 상향 언급에도 불구하고, 매도 타이밍, 쓰레기 주식 등 부정적 의견 지배적.</t>
+          <t>투자주의 해제 및 대량 거래량 흡수에도 불구하고 주가 변동성 및 하락세 지속. 향후 1000만주 거래량 시 20% 상승 기대.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['LNG선', '수주', '목표주가']</t>
+          <t>['투자주의', '거래량', '변동성']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10440</v>
+        <v>20250</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.06%</t>
+          <t>'-2.17%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1.29</v>
+        <v>-0.39</v>
       </c>
       <c r="E18" t="n">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="F18" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="G18" t="n">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="H18" t="n">
-        <v>19.22</v>
+        <v>28.51</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,47 +2067,47 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>10660</v>
+        <v>20700</v>
       </c>
       <c r="K18" t="n">
-        <v>10500</v>
+        <v>20750</v>
       </c>
       <c r="L18" t="n">
-        <v>10900</v>
+        <v>20750</v>
       </c>
       <c r="M18" t="n">
-        <v>10060</v>
+        <v>20250</v>
       </c>
       <c r="N18" t="n">
-        <v>17.93</v>
+        <v>28.9</v>
       </c>
       <c r="O18" t="n">
-        <v>115356178985</v>
+        <v>24296756600</v>
       </c>
       <c r="P18" t="n">
-        <v>22450</v>
+        <v>35350</v>
       </c>
       <c r="Q18" t="n">
-        <v>1760</v>
+        <v>18440</v>
       </c>
       <c r="R18" t="n">
-        <v>-475000</v>
+        <v>-677000</v>
       </c>
       <c r="S18" t="n">
-        <v>2000</v>
+        <v>-51000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>300만주 흡수 후 급등 가능성 언급. 기타법인 매도 및 투자주의 해제 예정.</t>
+          <t>LNG선 1.6조 수주 및 상선 목표치 초과 달성. IBK투자증권 목표주가 3만7000원 제시. 시장 침체 및 공매도 심화 우려.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['거래량', '투자주의']</t>
+          <t>['LNG선 수주', '목표주가', '공매도']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -2142,13 +2142,13 @@
         <v>-0.08</v>
       </c>
       <c r="E19" t="n">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="F19" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G19" t="n">
-        <v>817</v>
+        <v>832</v>
       </c>
       <c r="H19" t="n">
         <v>23.37</v>
@@ -2174,7 +2174,7 @@
         <v>23.45</v>
       </c>
       <c r="O19" t="n">
-        <v>121410895800</v>
+        <v>123625041900</v>
       </c>
       <c r="P19" t="n">
         <v>139200</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>웨스팅하우스 지분 인수 이슈에 대한 기대감과 공매도 세력에 대한 부정적 언급 공존. 상반된 전망 제시.</t>
+          <t>웨스팅하우스 지분 인수 및 경영권 참여 기대감 속 공매도 세력과의 갈등. 정치적 불확실성 및 정부 정책에 대한 불신.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['웨스팅하우스', '공매도', '지분 인수']</t>
+          <t>['웨스팅하우스', '지분 인수', '공매도']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31550</v>
+        <v>31600</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-2.77%</t>
+          <t>'-2.62%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.34</v>
       </c>
       <c r="E20" t="n">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F20" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G20" t="n">
-        <v>1116</v>
+        <v>1121</v>
       </c>
       <c r="H20" t="n">
         <v>17.16</v>
@@ -2266,7 +2266,7 @@
         <v>17.5</v>
       </c>
       <c r="O20" t="n">
-        <v>8549575200</v>
+        <v>8620694150</v>
       </c>
       <c r="P20" t="n">
         <v>69200</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>유럽 담관암 신약 신청 관련 불확실성 속 FDA 실패 가능성 제기. 과거 신약 실패 경험과 공모주 청약 시점의 유럽 신청에 대한 의구심이 공존.</t>
+          <t>담관암, 간암 FDA 순차 승인 기대감 속, 유럽 신약 신청 시점에 대한 의구심 및 과거 실패 사례 언급.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['담관암', 'FDA', '신약 신청']</t>
+          <t>['FDA', '신약', '담관암']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2311,31 +2311,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>한컴위드</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5080</v>
+        <v>17060</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-2.87%</t>
+          <t>'-2.79%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-1.39</v>
+        <v>0.1</v>
       </c>
       <c r="E21" t="n">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="F21" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="G21" t="n">
-        <v>173</v>
+        <v>331</v>
       </c>
       <c r="H21" t="n">
-        <v>1.29</v>
+        <v>0.45</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,51 +2343,51 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>5230</v>
+        <v>17550</v>
       </c>
       <c r="K21" t="n">
-        <v>5750</v>
+        <v>17150</v>
       </c>
       <c r="L21" t="n">
-        <v>5880</v>
+        <v>18860</v>
       </c>
       <c r="M21" t="n">
-        <v>5020</v>
+        <v>16710</v>
       </c>
       <c r="N21" t="n">
-        <v>2.68</v>
+        <v>0.35</v>
       </c>
       <c r="O21" t="n">
-        <v>62008715500</v>
+        <v>157797586310</v>
       </c>
       <c r="P21" t="n">
-        <v>8980</v>
+        <v>30550</v>
       </c>
       <c r="Q21" t="n">
-        <v>2795</v>
+        <v>6100</v>
       </c>
       <c r="R21" t="n">
-        <v>98000</v>
+        <v>-14000</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>미국 사이버 보안주 강세 및 양자 보안 관련 기술 분석. 허매수 및 급등 가능성 언급.</t>
+          <t>미국 보안주 강세 속에서 주가 하락에 대한 불만과 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['사이버 보안', '양자 보안', '기술 분석']</t>
+          <t>['보안주', '개미털기', '주가조작']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,38 +2396,38 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>054920</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>한컴위드</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17020</v>
+        <v>5080</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-3.02%</t>
+          <t>'-2.87%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.1</v>
+        <v>-1.39</v>
       </c>
       <c r="E22" t="n">
-        <v>168</v>
+        <v>85</v>
       </c>
       <c r="F22" t="n">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="G22" t="n">
-        <v>329</v>
+        <v>170</v>
       </c>
       <c r="H22" t="n">
-        <v>0.45</v>
+        <v>1.29</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,51 +2435,51 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>17550</v>
+        <v>5230</v>
       </c>
       <c r="K22" t="n">
-        <v>17150</v>
+        <v>5750</v>
       </c>
       <c r="L22" t="n">
-        <v>18860</v>
+        <v>5880</v>
       </c>
       <c r="M22" t="n">
-        <v>16710</v>
+        <v>5020</v>
       </c>
       <c r="N22" t="n">
-        <v>0.35</v>
+        <v>2.68</v>
       </c>
       <c r="O22" t="n">
-        <v>157464774830</v>
+        <v>62172640220</v>
       </c>
       <c r="P22" t="n">
-        <v>30550</v>
+        <v>8980</v>
       </c>
       <c r="Q22" t="n">
-        <v>6100</v>
+        <v>2795</v>
       </c>
       <c r="R22" t="n">
-        <v>-14000</v>
+        <v>98000</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>미국 보안주 강세 속에서 주가 하락에 대한 불만과 조작 의혹 제기.</t>
+          <t>미국 보안주 상승에 따른 양자보안 관련 기대감 속, 주가 바닥론 제기. 일부 투자자 매도세 및 의구심 존재.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['보안주', '개미털기', '주가조작']</t>
+          <t>['양자보안', '사이버보안', '기술적 분석']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>054920</t>
         </is>
       </c>
     </row>
@@ -2499,18 +2499,18 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5890</v>
+        <v>5910</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-6.66%</t>
+          <t>'-6.34%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>-2.04</v>
       </c>
       <c r="E23" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F23" t="n">
         <v>53</v>
@@ -2542,7 +2542,7 @@
         <v>3.02</v>
       </c>
       <c r="O23" t="n">
-        <v>41444123125</v>
+        <v>41654290435</v>
       </c>
       <c r="P23" t="n">
         <v>11370</v>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>13950</v>
+        <v>13990</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-6.88%</t>
+          <t>'-6.61%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="F24" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G24" t="n">
-        <v>551</v>
+        <v>582</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -2634,7 +2634,7 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>32732347120</v>
+        <v>32917192390</v>
       </c>
       <c r="P24" t="n">
         <v>36200</v>
@@ -2650,16 +2650,16 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>국제 유가 상승 및 미장 에너지주 폭등 관련 언급. 비축유 및 이란 관련 이슈로 급락 가능성 경고.</t>
+          <t>국제유가 상승 및 미국 에너지주 폭등에 따른 기대감. 그러나 비축유 이슈 및 FOMC 대비 경계감 존재.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['국제 유가', '비축유', '급락']</t>
+          <t>['국제유가', '에너지주', 'FOMC']</t>
         </is>
       </c>
       <c r="X24" t="n">

--- a/data/trending_integrated_20260916_13.xlsx
+++ b/data/trending_integrated_20260916_13.xlsx
@@ -584,7 +584,7 @@
         <v>149</v>
       </c>
       <c r="G2" t="n">
-        <v>1106</v>
+        <v>1127</v>
       </c>
       <c r="H2" t="n">
         <v>1.03</v>
@@ -610,7 +610,7 @@
         <v>2.24</v>
       </c>
       <c r="O2" t="n">
-        <v>7432065090</v>
+        <v>7435432770</v>
       </c>
       <c r="P2" t="n">
         <v>6900</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>카카오의 잠재적 인수 및 합법 카지노 사업 확장 기대감에 따른 주가 상승 전망. 클래리티법 부결은 무관.</t>
+          <t>카카오 인수 관련 합법 카지노 사업 확대 기대감. 공매도 숏스퀴즈 전망 및 본느 7연상 기록 경신 가능성 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['카카오 인수', '합법 카지노', '숏스퀴즈']</t>
+          <t>['카카오', '인수', '공매도']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,21 +659,21 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13540</v>
+        <v>13680</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+26.54%</t>
+          <t>'+27.85%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F3" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G3" t="n">
         <v>95</v>
@@ -702,7 +702,7 @@
         <v>0.42</v>
       </c>
       <c r="O3" t="n">
-        <v>173677679120</v>
+        <v>174788629155</v>
       </c>
       <c r="P3" t="n">
         <v>25700</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16100</v>
+        <v>16210</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.86%</t>
+          <t>'+14.64%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.15</v>
       </c>
       <c r="E4" t="n">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="F4" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G4" t="n">
-        <v>1681</v>
+        <v>1750</v>
       </c>
       <c r="H4" t="n">
         <v>1.95</v>
@@ -794,7 +794,7 @@
         <v>1.8</v>
       </c>
       <c r="O4" t="n">
-        <v>569527308215</v>
+        <v>579513869265</v>
       </c>
       <c r="P4" t="n">
         <v>31500</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>외국인/기관 600억 대량 순매수 및 미국 자회사 대규모 광통신 수주. 10만원 목표 주가 제시 및 우상향 추세 전망.</t>
+          <t>미국 자회사 대규모 광통신 수주 뉴스 기반 상승. 외국인/기관 대량 순매수.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['외국인 순매수', '광통신 수주', '대장주']</t>
+          <t>['광통신', '수주', '순매수']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4475</v>
+        <v>4455</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.62%</t>
+          <t>'+8.13%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.03</v>
       </c>
       <c r="E5" t="n">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="F5" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="G5" t="n">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="H5" t="n">
         <v>0.74</v>
@@ -886,7 +886,7 @@
         <v>0.77</v>
       </c>
       <c r="O5" t="n">
-        <v>306940089441</v>
+        <v>308496308903</v>
       </c>
       <c r="P5" t="n">
         <v>8100</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>광통신 섹터 상승 모멘텀과 연계된 기대감. 4천원 지지선 확보 및 대량 거래량 발생 시 20% 상승 가능성 언급.</t>
+          <t>광통신 관련 미장 상승 영향 및 젠슨 황 언급. 4천원 지지선 확보 후 추가 상승 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['광통신', '거래량', '지지선']</t>
+          <t>['광통신', '젠슨 황', '지지선']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4730</v>
+        <v>4735</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.11%</t>
+          <t>'+5.22%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.82</v>
       </c>
       <c r="E6" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F6" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G6" t="n">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="H6" t="n">
         <v>1.66</v>
@@ -978,7 +978,7 @@
         <v>0.84</v>
       </c>
       <c r="O6" t="n">
-        <v>120327661721</v>
+        <v>121753565250</v>
       </c>
       <c r="P6" t="n">
         <v>6190</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>삼성과 4381억 규모 공급 계약 체결 가능성 언급. 재료 기반 급등 기대감 및 주포의 단타 매매 의혹.</t>
+          <t>삼성전자 4381억 규모 공급 계약 체결. 매집 완료 후 재료 기반 상승 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['공급 계약', '주포', '재료']</t>
+          <t>['삼성전자', '공급 계약', '매집']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>194700</v>
+        <v>194400</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.06%</t>
+          <t>'+3.90%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F7" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G7" t="n">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="H7" t="n">
         <v>75.66</v>
@@ -1070,7 +1070,7 @@
         <v>75.67</v>
       </c>
       <c r="O7" t="n">
-        <v>474082253200</v>
+        <v>495413037850</v>
       </c>
       <c r="P7" t="n">
         <v>243500</v>
@@ -1115,184 +1115,184 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1749000</v>
+        <v>7140</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.49%</t>
+          <t>'+3.48%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>75</v>
       </c>
       <c r="F8" t="n">
-        <v>472</v>
+        <v>41</v>
       </c>
       <c r="G8" t="n">
-        <v>1984</v>
+        <v>61</v>
       </c>
       <c r="H8" t="n">
-        <v>50.2</v>
+        <v>0.79</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1690000</v>
+        <v>6900</v>
       </c>
       <c r="K8" t="n">
-        <v>1686000</v>
+        <v>6770</v>
       </c>
       <c r="L8" t="n">
-        <v>1750000</v>
+        <v>8590</v>
       </c>
       <c r="M8" t="n">
-        <v>1686000</v>
+        <v>6660</v>
       </c>
       <c r="N8" t="n">
-        <v>50.27</v>
+        <v>0.7</v>
       </c>
       <c r="O8" t="n">
-        <v>2909620347500</v>
+        <v>76083601940</v>
       </c>
       <c r="P8" t="n">
-        <v>2987000</v>
+        <v>10360</v>
       </c>
       <c r="Q8" t="n">
-        <v>331500</v>
+        <v>2965</v>
       </c>
       <c r="R8" t="n">
-        <v>-46000</v>
+        <v>74000</v>
       </c>
       <c r="S8" t="n">
-        <v>113000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>외인 선물 대량 매수 및 기관 자금 유입 기대감. 자사주 매입 및 소각 기대감으로 인한 상승 전망. 반도체 실적 발표 시즌.</t>
+          <t>보안 대장주로서의 지위 강조 및 AI 관련 논의 언급. 긍정적 흐름 기대.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['자사주 매입', '기관 매수', '반도체 실적']</t>
+          <t>['보안주', 'AI', '대장주']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>72</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7140</v>
+        <v>1742000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.48%</t>
+          <t>'+3.08%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.09</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>74</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>41</v>
+        <v>473</v>
       </c>
       <c r="G9" t="n">
-        <v>60</v>
+        <v>1985</v>
       </c>
       <c r="H9" t="n">
-        <v>0.79</v>
+        <v>50.2</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>6900</v>
+        <v>1690000</v>
       </c>
       <c r="K9" t="n">
-        <v>6770</v>
+        <v>1686000</v>
       </c>
       <c r="L9" t="n">
-        <v>8590</v>
+        <v>1750000</v>
       </c>
       <c r="M9" t="n">
-        <v>6660</v>
+        <v>1686000</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7</v>
+        <v>50.27</v>
       </c>
       <c r="O9" t="n">
-        <v>75955624390</v>
+        <v>3016101630500</v>
       </c>
       <c r="P9" t="n">
-        <v>10360</v>
+        <v>2987000</v>
       </c>
       <c r="Q9" t="n">
-        <v>2965</v>
+        <v>331500</v>
       </c>
       <c r="R9" t="n">
-        <v>74000</v>
+        <v>-46000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>113000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>보안 대장주로서의 지위 강조 및 AI 관련 논의 언급. 긍정적 흐름 기대.</t>
+          <t>젠슨 황 관련 기대감 및 자사주 매입·소각 기대감으로 인한 상승세. 반도체 실적 시즌 돌입.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['보안주', 'AI', '대장주']</t>
+          <t>['젠슨 황', '자사주', '반도체']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>72</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3620</v>
+        <v>3595</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.99%</t>
+          <t>'+2.28%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="F10" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G10" t="n">
-        <v>486</v>
+        <v>504</v>
       </c>
       <c r="H10" t="n">
         <v>3.11</v>
@@ -1340,13 +1340,13 @@
         <v>4140</v>
       </c>
       <c r="M10" t="n">
-        <v>3615</v>
+        <v>3565</v>
       </c>
       <c r="N10" t="n">
         <v>3.16</v>
       </c>
       <c r="O10" t="n">
-        <v>17200579208</v>
+        <v>17556405332</v>
       </c>
       <c r="P10" t="n">
         <v>16110</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>최대주주 유한양행 확인, 그러나 과거 급등 후 하락 및 재탕 뉴스에 대한 투자자 불신 심화.</t>
+          <t>기대와 달리 주가 하락 및 사기 도박판 의혹 제기. 재탕 뉴스에 대한 부정적 전망 및 매도 권유.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['바이오', '공매도', '최대주주']</t>
+          <t>['제약주', '바이오', '공매도']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>253500</v>
+        <v>252750</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.01%</t>
+          <t>'+1.71%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="G11" t="n">
-        <v>1403</v>
+        <v>1532</v>
       </c>
       <c r="H11" t="n">
         <v>46.56</v>
@@ -1438,7 +1438,7 @@
         <v>46.57</v>
       </c>
       <c r="O11" t="n">
-        <v>1732789971250</v>
+        <v>1785121065500</v>
       </c>
       <c r="P11" t="n">
         <v>374500</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>연말 최고점 돌파 기대감 속 정치적 이슈 및 시장 침체 우려 상존. 30조 배당 및 3분기 실적 호조 언급.</t>
+          <t>정치적 이슈와 맞물려 주가 변동성 확대. 외인 순매수 전환 시 상승 전망.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['반도체', '배당', '정치적 이슈']</t>
+          <t>['정치', '외인', '순매수']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13540</v>
+        <v>13520</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+1.80%</t>
+          <t>'+1.65%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F12" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G12" t="n">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>15796939880</v>
+        <v>16234382915</v>
       </c>
       <c r="P12" t="n">
         <v>19380</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3420</v>
+        <v>3400</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+1.79%</t>
+          <t>'+1.19%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-1.34</v>
       </c>
       <c r="E13" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F13" t="n">
         <v>56</v>
       </c>
       <c r="G13" t="n">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1622,7 +1622,7 @@
         <v>1.34</v>
       </c>
       <c r="O13" t="n">
-        <v>99827480227</v>
+        <v>101087192108</v>
       </c>
       <c r="P13" t="n">
         <v>5100</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>양자내성암호 행정명령 및 양자암호 해독키 독점 공급 기대감. 미국 광통신 보안주 상승 및 가벼운 주가 흐름.</t>
+          <t>양자내성암호, 양자보안 관련 트럼프 행정명령 수혜 기대. 대한광통신과 유사한 흐름.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['양자암호', '보안주', '독점 공급']</t>
+          <t>['양자암호', '보안', '트럼프']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10150</v>
+        <v>10200</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.30%</t>
+          <t>'+0.79%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F14" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G14" t="n">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="H14" t="n">
         <v>0.67</v>
@@ -1714,7 +1714,7 @@
         <v>0.6</v>
       </c>
       <c r="O14" t="n">
-        <v>114536701885</v>
+        <v>115458791175</v>
       </c>
       <c r="P14" t="n">
         <v>15960</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미프진 독점 공급 계약 및 내년 1분기 도입 소식 기반 기대감. 재료 소멸 논쟁 상존.</t>
+          <t>미프진 독점 공급 계약 관련 도입 시점 불확실 속 기대감 혼재. 주가 변동성 큼.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['미프진', '독점 공급', '재료 소멸']</t>
+          <t>['미프진', '독점 공급', '도입']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8500</v>
+        <v>8510</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.28%</t>
+          <t>'-1.16%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.5</v>
       </c>
       <c r="E15" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F15" t="n">
         <v>57</v>
       </c>
       <c r="G15" t="n">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="H15" t="n">
         <v>26.66</v>
@@ -1806,7 +1806,7 @@
         <v>27.16</v>
       </c>
       <c r="O15" t="n">
-        <v>10976419430</v>
+        <v>11093050160</v>
       </c>
       <c r="P15" t="n">
         <v>17950</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>삼성디스플레이와의 비교 언급 및 FLiPP 양산 기대감 있으나, 재무 상태, 외인 매도세, 경영진 관련 부정적 의견 다수.</t>
+          <t>경영진 성과급 논란 및 재무 구조 악화 우려. 삼성디스플레이와의 비교 속 주가 부진.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['FLiPP', '재무', '외인 매도']</t>
+          <t>['재무 구조', '경영진', '삼성디스플레이']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1851,31 +1851,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18780</v>
+        <v>10480</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.83%</t>
+          <t>'-1.69%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.11</v>
+        <v>1.29</v>
       </c>
       <c r="E16" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="F16" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G16" t="n">
-        <v>400</v>
+        <v>167</v>
       </c>
       <c r="H16" t="n">
-        <v>10.64</v>
+        <v>19.22</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>19130</v>
+        <v>10660</v>
       </c>
       <c r="K16" t="n">
-        <v>19160</v>
+        <v>10500</v>
       </c>
       <c r="L16" t="n">
-        <v>19340</v>
+        <v>10900</v>
       </c>
       <c r="M16" t="n">
-        <v>18330</v>
+        <v>10060</v>
       </c>
       <c r="N16" t="n">
-        <v>10.53</v>
+        <v>17.93</v>
       </c>
       <c r="O16" t="n">
-        <v>49382161465</v>
+        <v>116483634360</v>
       </c>
       <c r="P16" t="n">
-        <v>40350</v>
+        <v>22450</v>
       </c>
       <c r="Q16" t="n">
-        <v>3320</v>
+        <v>1760</v>
       </c>
       <c r="R16" t="n">
-        <v>-116000</v>
+        <v>-475000</v>
       </c>
       <c r="S16" t="n">
-        <v>-90000</v>
+        <v>2000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>대차해지 운동 독려와 함께 주가조작 의혹 제기. 대형 계약 임박 및 10만원 이상 목표가 언급.</t>
+          <t>연기금 순매수세 유입. 투주 물량 소화 중이나 주가 상승 모멘텀 불확실.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['대차해지', '주가조작', '대형 계약']</t>
+          <t>['연기금', '순매수', '투주']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10450</v>
+        <v>20250</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.97%</t>
+          <t>'-2.17%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.29</v>
+        <v>-0.39</v>
       </c>
       <c r="E17" t="n">
-        <v>99</v>
+        <v>134</v>
       </c>
       <c r="F17" t="n">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G17" t="n">
-        <v>164</v>
+        <v>329</v>
       </c>
       <c r="H17" t="n">
-        <v>19.22</v>
+        <v>28.51</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,47 +1975,47 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>10660</v>
+        <v>20700</v>
       </c>
       <c r="K17" t="n">
-        <v>10500</v>
+        <v>20750</v>
       </c>
       <c r="L17" t="n">
-        <v>10900</v>
+        <v>20750</v>
       </c>
       <c r="M17" t="n">
-        <v>10060</v>
+        <v>20250</v>
       </c>
       <c r="N17" t="n">
-        <v>17.93</v>
+        <v>28.9</v>
       </c>
       <c r="O17" t="n">
-        <v>115943796025</v>
+        <v>25003452625</v>
       </c>
       <c r="P17" t="n">
-        <v>22450</v>
+        <v>35350</v>
       </c>
       <c r="Q17" t="n">
-        <v>1760</v>
+        <v>18440</v>
       </c>
       <c r="R17" t="n">
-        <v>-475000</v>
+        <v>-677000</v>
       </c>
       <c r="S17" t="n">
-        <v>2000</v>
+        <v>-51000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>투자주의 해제 및 대량 거래량 흡수에도 불구하고 주가 변동성 및 하락세 지속. 향후 1000만주 거래량 시 20% 상승 기대.</t>
+          <t>LNG선 1.6조 수주 및 상선 목표치 초과 달성. IBK투자증권 목표주가 3만7000원 제시. 시장 침체 및 공매도 심화 우려.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['투자주의', '거래량', '변동성']</t>
+          <t>['LNG선 수주', '목표주가', '공매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20250</v>
+        <v>18700</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.17%</t>
+          <t>'-2.25%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.39</v>
+        <v>0.11</v>
       </c>
       <c r="E18" t="n">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="F18" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="G18" t="n">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="H18" t="n">
-        <v>28.51</v>
+        <v>10.64</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,38 +2067,38 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>20700</v>
+        <v>19130</v>
       </c>
       <c r="K18" t="n">
-        <v>20750</v>
+        <v>19160</v>
       </c>
       <c r="L18" t="n">
-        <v>20750</v>
+        <v>19340</v>
       </c>
       <c r="M18" t="n">
-        <v>20250</v>
+        <v>18330</v>
       </c>
       <c r="N18" t="n">
-        <v>28.9</v>
+        <v>10.53</v>
       </c>
       <c r="O18" t="n">
-        <v>24296756600</v>
+        <v>50517409345</v>
       </c>
       <c r="P18" t="n">
-        <v>35350</v>
+        <v>40350</v>
       </c>
       <c r="Q18" t="n">
-        <v>18440</v>
+        <v>3320</v>
       </c>
       <c r="R18" t="n">
-        <v>-677000</v>
+        <v>-116000</v>
       </c>
       <c r="S18" t="n">
-        <v>-51000</v>
+        <v>-90000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>LNG선 1.6조 수주 및 상선 목표치 초과 달성. IBK투자증권 목표주가 3만7000원 제시. 시장 침체 및 공매도 심화 우려.</t>
+          <t>대차해지 운동 독려와 함께 주가조작 의혹 제기. 대형 계약 임박 및 10만원 이상 목표가 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['LNG선 수주', '목표주가', '공매도']</t>
+          <t>['대차해지', '주가조작', '대형 계약']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>84200</v>
+        <v>84150</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.32%</t>
+          <t>'-2.38%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.08</v>
       </c>
       <c r="E19" t="n">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F19" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G19" t="n">
-        <v>832</v>
+        <v>868</v>
       </c>
       <c r="H19" t="n">
         <v>23.37</v>
@@ -2174,7 +2174,7 @@
         <v>23.45</v>
       </c>
       <c r="O19" t="n">
-        <v>123625041900</v>
+        <v>126586024350</v>
       </c>
       <c r="P19" t="n">
         <v>139200</v>
@@ -2190,12 +2190,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>웨스팅하우스 지분 인수 및 경영권 참여 기대감 속 공매도 세력과의 갈등. 정치적 불확실성 및 정부 정책에 대한 불신.</t>
+          <t>웨스팅하우스 지분 인수 기대감 있으나 공매도 공세 및 대미투자 연기 이슈로 주가 하락.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31600</v>
+        <v>31550</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-2.62%</t>
+          <t>'-2.77%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.34</v>
       </c>
       <c r="E20" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="F20" t="n">
         <v>133</v>
       </c>
       <c r="G20" t="n">
-        <v>1121</v>
+        <v>1129</v>
       </c>
       <c r="H20" t="n">
         <v>17.16</v>
@@ -2266,7 +2266,7 @@
         <v>17.5</v>
       </c>
       <c r="O20" t="n">
-        <v>8620694150</v>
+        <v>8684522350</v>
       </c>
       <c r="P20" t="n">
         <v>69200</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17060</v>
+        <v>17030</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-2.79%</t>
+          <t>'-2.96%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.1</v>
       </c>
       <c r="E21" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F21" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G21" t="n">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="H21" t="n">
         <v>0.45</v>
@@ -2358,7 +2358,7 @@
         <v>0.35</v>
       </c>
       <c r="O21" t="n">
-        <v>157797586310</v>
+        <v>158122665745</v>
       </c>
       <c r="P21" t="n">
         <v>30550</v>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>미국 보안주 강세 속에서 주가 하락에 대한 불만과 조작 의혹 제기.</t>
+          <t>미국 보안주 상승에도 불구하고 인위적 하락 의혹 제기. 단기 22,000원 및 20,000원 트라이 전망.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['보안주', '개미털기', '주가조작']</t>
+          <t>['보안주', '매출', '하락']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5080</v>
+        <v>5070</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-2.87%</t>
+          <t>'-3.06%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-1.39</v>
       </c>
       <c r="E22" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F22" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G22" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H22" t="n">
         <v>1.29</v>
@@ -2450,7 +2450,7 @@
         <v>2.68</v>
       </c>
       <c r="O22" t="n">
-        <v>62172640220</v>
+        <v>62333358595</v>
       </c>
       <c r="P22" t="n">
         <v>8980</v>
@@ -2499,11 +2499,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5910</v>
+        <v>5920</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-6.34%</t>
+          <t>'-6.18%</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2542,7 +2542,7 @@
         <v>3.02</v>
       </c>
       <c r="O23" t="n">
-        <v>41654290435</v>
+        <v>41870415005</v>
       </c>
       <c r="P23" t="n">
         <v>11370</v>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>13990</v>
+        <v>14010</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-6.61%</t>
+          <t>'-6.48%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F24" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G24" t="n">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -2634,7 +2634,7 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>32917192390</v>
+        <v>33310178940</v>
       </c>
       <c r="P24" t="n">
         <v>36200</v>

--- a/data/trending_integrated_20260916_13.xlsx
+++ b/data/trending_integrated_20260916_13.xlsx
@@ -578,13 +578,13 @@
         <v>-1.21</v>
       </c>
       <c r="E2" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F2" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G2" t="n">
-        <v>1127</v>
+        <v>1142</v>
       </c>
       <c r="H2" t="n">
         <v>1.03</v>
@@ -610,7 +610,7 @@
         <v>2.24</v>
       </c>
       <c r="O2" t="n">
-        <v>7435432770</v>
+        <v>7446434370</v>
       </c>
       <c r="P2" t="n">
         <v>6900</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>카카오 인수 관련 합법 카지노 사업 확대 기대감. 공매도 숏스퀴즈 전망 및 본느 7연상 기록 경신 가능성 언급.</t>
+          <t>카카오의 인수 가능성 및 합법 카지노 사업 확장 기대. 본느 7연상 패턴 돌파 및 숏스퀴즈 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['카카오', '인수', '공매도']</t>
+          <t>['카카오 인수', '합법 카지노', '숏스퀴즈']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13680</v>
+        <v>13670</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+27.85%</t>
+          <t>'+27.76%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F3" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G3" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H3" t="n">
         <v>0.4</v>
@@ -702,7 +702,7 @@
         <v>0.42</v>
       </c>
       <c r="O3" t="n">
-        <v>174788629155</v>
+        <v>175168035975</v>
       </c>
       <c r="P3" t="n">
         <v>25700</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>6G 통신 테마주 언급. 거래량 증가 및 급등 가능성 기대.</t>
+          <t>삼성과 4381억 원 공급 계약 관련 언급. 역대급 거래량 발생 및 6G 통신 대장주로서의 가능성.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['6G 통신', '거래량', '급등']</t>
+          <t>['공급 계약', '삼성', '6G 통신']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16210</v>
+        <v>16230</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.64%</t>
+          <t>'+14.78%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.15</v>
       </c>
       <c r="E4" t="n">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="F4" t="n">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="G4" t="n">
-        <v>1750</v>
+        <v>1812</v>
       </c>
       <c r="H4" t="n">
         <v>1.95</v>
@@ -794,7 +794,7 @@
         <v>1.8</v>
       </c>
       <c r="O4" t="n">
-        <v>579513869265</v>
+        <v>588448160555</v>
       </c>
       <c r="P4" t="n">
         <v>31500</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 자회사 대규모 광통신 수주 뉴스 기반 상승. 외국인/기관 대량 순매수.</t>
+          <t>외국인/기관 600억 대량 순매수 및 미국 자회사 대규모 수주 기대. 16500원 돌파 및 10만 원 상승 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['광통신', '수주', '순매수']</t>
+          <t>['외국인 순매수', '미국 자회사', '대규모 수주']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4455</v>
+        <v>4425</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.13%</t>
+          <t>'+7.40%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.03</v>
       </c>
       <c r="E5" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="F5" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G5" t="n">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="H5" t="n">
         <v>0.74</v>
@@ -886,7 +886,7 @@
         <v>0.77</v>
       </c>
       <c r="O5" t="n">
-        <v>308496308903</v>
+        <v>309669222307</v>
       </c>
       <c r="P5" t="n">
         <v>8100</v>
@@ -946,13 +946,13 @@
         <v>0.82</v>
       </c>
       <c r="E6" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F6" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G6" t="n">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="H6" t="n">
         <v>1.66</v>
@@ -978,7 +978,7 @@
         <v>0.84</v>
       </c>
       <c r="O6" t="n">
-        <v>121753565250</v>
+        <v>122486628303</v>
       </c>
       <c r="P6" t="n">
         <v>6190</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>삼성전자 4381억 규모 공급 계약 체결. 매집 완료 후 재료 기반 상승 전망.</t>
+          <t>삼성과 4381억 원 규모 공급 계약 체결. 잠재력 및 재료 보유 종목으로 10000원 직행 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['삼성전자', '공급 계약', '매집']</t>
+          <t>['공급 계약', '삼성', '잠재력']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>194400</v>
+        <v>194300</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+3.90%</t>
+          <t>'+3.85%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F7" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G7" t="n">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="H7" t="n">
         <v>75.66</v>
@@ -1070,7 +1070,7 @@
         <v>75.67</v>
       </c>
       <c r="O7" t="n">
-        <v>495413037850</v>
+        <v>503831926650</v>
       </c>
       <c r="P7" t="n">
         <v>243500</v>
@@ -1136,7 +1136,7 @@
         <v>41</v>
       </c>
       <c r="G8" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H8" t="n">
         <v>0.79</v>
@@ -1162,7 +1162,7 @@
         <v>0.7</v>
       </c>
       <c r="O8" t="n">
-        <v>76083601940</v>
+        <v>76165846855</v>
       </c>
       <c r="P8" t="n">
         <v>10360</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1742000</v>
+        <v>1743000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.08%</t>
+          <t>'+3.14%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="G9" t="n">
-        <v>1985</v>
+        <v>2004</v>
       </c>
       <c r="H9" t="n">
         <v>50.2</v>
@@ -1254,7 +1254,7 @@
         <v>50.27</v>
       </c>
       <c r="O9" t="n">
-        <v>3016101630500</v>
+        <v>3110017203000</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>젠슨 황 관련 기대감 및 자사주 매입·소각 기대감으로 인한 상승세. 반도체 실적 시즌 돌입.</t>
+          <t>젠슨 황 관련 언급과 함께 외인 선물 매수세 유입. 자사주 매입 및 소각 기대감 속에 240만 원 목표.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['젠슨 황', '자사주', '반도체']</t>
+          <t>['젠슨 황', '자사주 매입', '외인 선물']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3595</v>
+        <v>3425</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.28%</t>
+          <t>'+1.93%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.05</v>
+        <v>-1.34</v>
       </c>
       <c r="E10" t="n">
-        <v>133</v>
+        <v>87</v>
       </c>
       <c r="F10" t="n">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="G10" t="n">
-        <v>504</v>
+        <v>189</v>
       </c>
       <c r="H10" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>3515</v>
+        <v>3360</v>
       </c>
       <c r="K10" t="n">
-        <v>4120</v>
+        <v>3570</v>
       </c>
       <c r="L10" t="n">
-        <v>4140</v>
+        <v>3910</v>
       </c>
       <c r="M10" t="n">
-        <v>3565</v>
+        <v>3345</v>
       </c>
       <c r="N10" t="n">
-        <v>3.16</v>
+        <v>1.34</v>
       </c>
       <c r="O10" t="n">
-        <v>17556405332</v>
+        <v>101767807605</v>
       </c>
       <c r="P10" t="n">
-        <v>16110</v>
+        <v>5100</v>
       </c>
       <c r="Q10" t="n">
-        <v>2300</v>
+        <v>966</v>
       </c>
       <c r="R10" t="n">
-        <v>-386000</v>
+        <v>-31000</v>
       </c>
       <c r="S10" t="n">
-        <v>-206000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>기대와 달리 주가 하락 및 사기 도박판 의혹 제기. 재탕 뉴스에 대한 부정적 전망 및 매도 권유.</t>
+          <t>양자내성암호, 양자보안 관련 트럼프 행정명령 수혜 기대. 대한광통신과 유사한 흐름.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['제약주', '바이오', '공매도']</t>
+          <t>['양자암호', '보안', '트럼프']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,77 +1384,77 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>424870</t>
+          <t>062970</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>252750</v>
+        <v>3580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.71%</t>
+          <t>'+1.85%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>135</v>
       </c>
       <c r="F11" t="n">
-        <v>448</v>
+        <v>78</v>
       </c>
       <c r="G11" t="n">
-        <v>1532</v>
+        <v>523</v>
       </c>
       <c r="H11" t="n">
-        <v>46.56</v>
+        <v>3.11</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>248500</v>
+        <v>3515</v>
       </c>
       <c r="K11" t="n">
-        <v>248000</v>
+        <v>4120</v>
       </c>
       <c r="L11" t="n">
-        <v>254000</v>
+        <v>4140</v>
       </c>
       <c r="M11" t="n">
-        <v>247500</v>
+        <v>3565</v>
       </c>
       <c r="N11" t="n">
-        <v>46.57</v>
+        <v>3.16</v>
       </c>
       <c r="O11" t="n">
-        <v>1785121065500</v>
+        <v>17716983183</v>
       </c>
       <c r="P11" t="n">
-        <v>374500</v>
+        <v>16110</v>
       </c>
       <c r="Q11" t="n">
-        <v>76700</v>
+        <v>2300</v>
       </c>
       <c r="R11" t="n">
-        <v>-720000</v>
+        <v>-386000</v>
       </c>
       <c r="S11" t="n">
-        <v>754000</v>
+        <v>-206000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>정치적 이슈와 맞물려 주가 변동성 확대. 외인 순매수 전환 시 상승 전망.</t>
+          <t>최대주주가 유한양행이라는 언급이 있으나, 글쓴이는 사기 도박판이라 주장하며 투자 주의를 당부함. 공매도 및 개폭락 시작 가능성을 언급하며 반등 시 정리하라고 권고함.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['정치', '외인', '순매수']</t>
+          <t>['최대주주', '공매도', '개폭락']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>107</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>424870</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13520</v>
+        <v>252500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+1.65%</t>
+          <t>'+1.61%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>55</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>41</v>
+        <v>450</v>
       </c>
       <c r="G12" t="n">
-        <v>259</v>
+        <v>1496</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>46.56</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,152 +1515,152 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>13300</v>
+        <v>248500</v>
       </c>
       <c r="K12" t="n">
-        <v>13490</v>
+        <v>248000</v>
       </c>
       <c r="L12" t="n">
-        <v>13940</v>
+        <v>254000</v>
       </c>
       <c r="M12" t="n">
-        <v>13230</v>
+        <v>247500</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>46.57</v>
       </c>
       <c r="O12" t="n">
-        <v>16234382915</v>
+        <v>1846632056250</v>
       </c>
       <c r="P12" t="n">
-        <v>19380</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>3200</v>
+        <v>76700</v>
       </c>
       <c r="R12" t="n">
-        <v>-1000</v>
+        <v>-720000</v>
       </c>
       <c r="S12" t="n">
-        <v>4000</v>
+        <v>754000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>주가 하락 및 부진한 흐름에 대한 불만 토로, 영양가 없는 호재 언급. 투자 심리 위축.</t>
+          <t>정치적 이슈와 외부 요인 언급 속에 연말 최고점 돌파 기대. 외인 현물 순매수 전환 시 상승 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['주가', '호재', '투자심리']</t>
+          <t>['외인 순매수', '연말 전망', '정치 이슈']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>54</v>
+        <v>107</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>한국첨단소재</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3400</v>
+        <v>13500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+1.19%</t>
+          <t>'+1.50%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-1.34</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="F13" t="n">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="G13" t="n">
-        <v>189</v>
+        <v>263</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>3360</v>
+        <v>13300</v>
       </c>
       <c r="K13" t="n">
-        <v>3570</v>
+        <v>13490</v>
       </c>
       <c r="L13" t="n">
-        <v>3910</v>
+        <v>13940</v>
       </c>
       <c r="M13" t="n">
-        <v>3345</v>
+        <v>13230</v>
       </c>
       <c r="N13" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>101087192108</v>
+        <v>16506694435</v>
       </c>
       <c r="P13" t="n">
-        <v>5100</v>
+        <v>19380</v>
       </c>
       <c r="Q13" t="n">
-        <v>966</v>
+        <v>3200</v>
       </c>
       <c r="R13" t="n">
-        <v>-31000</v>
+        <v>-1000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>양자내성암호, 양자보안 관련 트럼프 행정명령 수혜 기대. 대한광통신과 유사한 흐름.</t>
+          <t>주가 하락 및 부진한 흐름에 대한 불만 토로, 영양가 없는 호재 언급. 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['양자암호', '보안', '트럼프']</t>
+          <t>['주가', '호재', '투자심리']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>062970</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10200</v>
+        <v>10140</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.79%</t>
+          <t>'+0.20%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F14" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G14" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H14" t="n">
         <v>0.67</v>
@@ -1714,7 +1714,7 @@
         <v>0.6</v>
       </c>
       <c r="O14" t="n">
-        <v>115458791175</v>
+        <v>115842697890</v>
       </c>
       <c r="P14" t="n">
         <v>15960</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8510</v>
+        <v>8500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.16%</t>
+          <t>'-1.28%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.5</v>
       </c>
       <c r="E15" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F15" t="n">
         <v>57</v>
       </c>
       <c r="G15" t="n">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H15" t="n">
         <v>26.66</v>
@@ -1806,7 +1806,7 @@
         <v>27.16</v>
       </c>
       <c r="O15" t="n">
-        <v>11093050160</v>
+        <v>11696941135</v>
       </c>
       <c r="P15" t="n">
         <v>17950</v>
@@ -1851,83 +1851,83 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>한컴위드</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10480</v>
+        <v>5145</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.69%</t>
+          <t>'-1.63%</t>
         </is>
       </c>
       <c r="D16" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="E16" t="n">
+        <v>87</v>
+      </c>
+      <c r="F16" t="n">
+        <v>50</v>
+      </c>
+      <c r="G16" t="n">
+        <v>176</v>
+      </c>
+      <c r="H16" t="n">
         <v>1.29</v>
       </c>
-      <c r="E16" t="n">
-        <v>100</v>
-      </c>
-      <c r="F16" t="n">
-        <v>63</v>
-      </c>
-      <c r="G16" t="n">
-        <v>167</v>
-      </c>
-      <c r="H16" t="n">
-        <v>19.22</v>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>10660</v>
+        <v>5230</v>
       </c>
       <c r="K16" t="n">
-        <v>10500</v>
+        <v>5750</v>
       </c>
       <c r="L16" t="n">
-        <v>10900</v>
+        <v>5880</v>
       </c>
       <c r="M16" t="n">
-        <v>10060</v>
+        <v>5020</v>
       </c>
       <c r="N16" t="n">
-        <v>17.93</v>
+        <v>2.68</v>
       </c>
       <c r="O16" t="n">
-        <v>116483634360</v>
+        <v>62659436545</v>
       </c>
       <c r="P16" t="n">
-        <v>22450</v>
+        <v>8980</v>
       </c>
       <c r="Q16" t="n">
-        <v>1760</v>
+        <v>2795</v>
       </c>
       <c r="R16" t="n">
-        <v>-475000</v>
+        <v>98000</v>
       </c>
       <c r="S16" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>연기금 순매수세 유입. 투주 물량 소화 중이나 주가 상승 모멘텀 불확실.</t>
+          <t>미국 사이버보안주 강세 속 양자보안 구축 의무화 및 3기업 독점 관련 기대.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['연기금', '순매수', '투주']</t>
+          <t>['양자보안', '사이버보안', '독점']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>054920</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20250</v>
+        <v>10460</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-2.17%</t>
+          <t>'-1.88%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.39</v>
+        <v>1.29</v>
       </c>
       <c r="E17" t="n">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="F17" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="G17" t="n">
-        <v>329</v>
+        <v>167</v>
       </c>
       <c r="H17" t="n">
-        <v>28.51</v>
+        <v>19.22</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,47 +1975,47 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>20700</v>
+        <v>10660</v>
       </c>
       <c r="K17" t="n">
-        <v>20750</v>
+        <v>10500</v>
       </c>
       <c r="L17" t="n">
-        <v>20750</v>
+        <v>10900</v>
       </c>
       <c r="M17" t="n">
-        <v>20250</v>
+        <v>10060</v>
       </c>
       <c r="N17" t="n">
-        <v>28.9</v>
+        <v>17.93</v>
       </c>
       <c r="O17" t="n">
-        <v>25003452625</v>
+        <v>116924229360</v>
       </c>
       <c r="P17" t="n">
-        <v>35350</v>
+        <v>22450</v>
       </c>
       <c r="Q17" t="n">
-        <v>18440</v>
+        <v>1760</v>
       </c>
       <c r="R17" t="n">
-        <v>-677000</v>
+        <v>-475000</v>
       </c>
       <c r="S17" t="n">
-        <v>-51000</v>
+        <v>2000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>LNG선 1.6조 수주 및 상선 목표치 초과 달성. IBK투자증권 목표주가 3만7000원 제시. 시장 침체 및 공매도 심화 우려.</t>
+          <t>연기금 순매수세 유입. 투주 물량 소화 중이나 주가 상승 모멘텀 불확실.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['LNG선 수주', '목표주가', '공매도']</t>
+          <t>['연기금', '순매수', '투주']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18700</v>
+        <v>18740</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.25%</t>
+          <t>'-2.04%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2056,7 +2056,7 @@
         <v>64</v>
       </c>
       <c r="G18" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H18" t="n">
         <v>10.64</v>
@@ -2082,7 +2082,7 @@
         <v>10.53</v>
       </c>
       <c r="O18" t="n">
-        <v>50517409345</v>
+        <v>51344890725</v>
       </c>
       <c r="P18" t="n">
         <v>40350</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>대차해지 운동 독려와 함께 주가조작 의혹 제기. 대형 계약 임박 및 10만원 이상 목표가 언급.</t>
+          <t>대차해지 운동 독려하며 주가 조작 의혹 제기. 2만 원 돌파 및 10만 원 이상 상승 기대.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['대차해지', '주가조작', '대형 계약']</t>
+          <t>['대차해지', '주가 조작', '대형 계약']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2127,31 +2127,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>84150</v>
+        <v>20225</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.38%</t>
+          <t>'-2.29%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.08</v>
+        <v>-0.39</v>
       </c>
       <c r="E19" t="n">
-        <v>275</v>
+        <v>136</v>
       </c>
       <c r="F19" t="n">
-        <v>145</v>
+        <v>77</v>
       </c>
       <c r="G19" t="n">
-        <v>868</v>
+        <v>340</v>
       </c>
       <c r="H19" t="n">
-        <v>23.37</v>
+        <v>28.51</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,51 +2159,51 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>86200</v>
+        <v>20700</v>
       </c>
       <c r="K19" t="n">
-        <v>86200</v>
+        <v>20750</v>
       </c>
       <c r="L19" t="n">
-        <v>86300</v>
+        <v>20750</v>
       </c>
       <c r="M19" t="n">
-        <v>83500</v>
+        <v>20200</v>
       </c>
       <c r="N19" t="n">
-        <v>23.45</v>
+        <v>28.9</v>
       </c>
       <c r="O19" t="n">
-        <v>126586024350</v>
+        <v>27518839175</v>
       </c>
       <c r="P19" t="n">
-        <v>139200</v>
+        <v>35350</v>
       </c>
       <c r="Q19" t="n">
-        <v>57000</v>
+        <v>18440</v>
       </c>
       <c r="R19" t="n">
-        <v>-102000</v>
+        <v>-677000</v>
       </c>
       <c r="S19" t="n">
-        <v>-86000</v>
+        <v>-51000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>웨스팅하우스 지분 인수 기대감 있으나 공매도 공세 및 대미투자 연기 이슈로 주가 하락.</t>
+          <t>1.6조 원 규모 LNG선 수주 소식. IBK투자증권 목표주가 3만7000원 제시 및 매수 투자의견.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['웨스팅하우스', '지분 인수', '공매도']</t>
+          <t>['LNG선 수주', 'IBK 목표주가', '공매도']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31550</v>
+        <v>31600</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-2.77%</t>
+          <t>'-2.62%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.34</v>
       </c>
       <c r="E20" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F20" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G20" t="n">
-        <v>1129</v>
+        <v>1137</v>
       </c>
       <c r="H20" t="n">
         <v>17.16</v>
@@ -2266,7 +2266,7 @@
         <v>17.5</v>
       </c>
       <c r="O20" t="n">
-        <v>8684522350</v>
+        <v>8794752900</v>
       </c>
       <c r="P20" t="n">
         <v>69200</v>
@@ -2311,83 +2311,83 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17030</v>
+        <v>83800</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-2.96%</t>
+          <t>'-2.78%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="E21" t="n">
-        <v>172</v>
+        <v>283</v>
       </c>
       <c r="F21" t="n">
-        <v>92</v>
+        <v>153</v>
       </c>
       <c r="G21" t="n">
-        <v>334</v>
+        <v>888</v>
       </c>
       <c r="H21" t="n">
-        <v>0.45</v>
+        <v>23.37</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>17550</v>
+        <v>86200</v>
       </c>
       <c r="K21" t="n">
-        <v>17150</v>
+        <v>86200</v>
       </c>
       <c r="L21" t="n">
-        <v>18860</v>
+        <v>86300</v>
       </c>
       <c r="M21" t="n">
-        <v>16710</v>
+        <v>83500</v>
       </c>
       <c r="N21" t="n">
-        <v>0.35</v>
+        <v>23.45</v>
       </c>
       <c r="O21" t="n">
-        <v>158122665745</v>
+        <v>129553893550</v>
       </c>
       <c r="P21" t="n">
-        <v>30550</v>
+        <v>139200</v>
       </c>
       <c r="Q21" t="n">
-        <v>6100</v>
+        <v>57000</v>
       </c>
       <c r="R21" t="n">
-        <v>-14000</v>
+        <v>-102000</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>-86000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>미국 보안주 상승에도 불구하고 인위적 하락 의혹 제기. 단기 22,000원 및 20,000원 트라이 전망.</t>
+          <t>웨스팅하우스 지분 인수 및 경영권 참여 가능성 언급. 공매도 세력과의 갈등 및 대미 투자 연기 이슈.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['보안주', '매출', '하락']</t>
+          <t>['웨스팅하우스', '공매도', '대미 투자']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,38 +2396,38 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>한컴위드</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5070</v>
+        <v>17000</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-3.06%</t>
+          <t>'-3.13%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-1.39</v>
+        <v>0.1</v>
       </c>
       <c r="E22" t="n">
-        <v>87</v>
+        <v>163</v>
       </c>
       <c r="F22" t="n">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="G22" t="n">
-        <v>175</v>
+        <v>331</v>
       </c>
       <c r="H22" t="n">
-        <v>1.29</v>
+        <v>0.45</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,51 +2435,51 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>5230</v>
+        <v>17550</v>
       </c>
       <c r="K22" t="n">
-        <v>5750</v>
+        <v>17150</v>
       </c>
       <c r="L22" t="n">
-        <v>5880</v>
+        <v>18860</v>
       </c>
       <c r="M22" t="n">
-        <v>5020</v>
+        <v>16710</v>
       </c>
       <c r="N22" t="n">
-        <v>2.68</v>
+        <v>0.35</v>
       </c>
       <c r="O22" t="n">
-        <v>62333358595</v>
+        <v>158297933885</v>
       </c>
       <c r="P22" t="n">
-        <v>8980</v>
+        <v>30550</v>
       </c>
       <c r="Q22" t="n">
-        <v>2795</v>
+        <v>6100</v>
       </c>
       <c r="R22" t="n">
-        <v>98000</v>
+        <v>-14000</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>미국 보안주 상승에 따른 양자보안 관련 기대감 속, 주가 바닥론 제기. 일부 투자자 매도세 및 의구심 존재.</t>
+          <t>미국 보안주 상승에도 불구하고 인위적 하락 의혹 제기. 단기 22,000원 및 20,000원 트라이 전망.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['양자보안', '사이버보안', '기술적 분석']</t>
+          <t>['보안주', '매출', '하락']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>054920</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2516,7 @@
         <v>53</v>
       </c>
       <c r="G23" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H23" t="n">
         <v>0.98</v>
@@ -2542,7 +2542,7 @@
         <v>3.02</v>
       </c>
       <c r="O23" t="n">
-        <v>41870415005</v>
+        <v>42199592825</v>
       </c>
       <c r="P23" t="n">
         <v>11370</v>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>14010</v>
+        <v>14020</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-6.48%</t>
+          <t>'-6.41%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="F24" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G24" t="n">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -2634,7 +2634,7 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>33310178940</v>
+        <v>33493899300</v>
       </c>
       <c r="P24" t="n">
         <v>36200</v>

--- a/data/trending_integrated_20260916_13.xlsx
+++ b/data/trending_integrated_20260916_13.xlsx
@@ -578,13 +578,13 @@
         <v>-1.21</v>
       </c>
       <c r="E2" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F2" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G2" t="n">
-        <v>1142</v>
+        <v>1146</v>
       </c>
       <c r="H2" t="n">
         <v>1.03</v>
@@ -610,7 +610,7 @@
         <v>2.24</v>
       </c>
       <c r="O2" t="n">
-        <v>7446434370</v>
+        <v>7452889410</v>
       </c>
       <c r="P2" t="n">
         <v>6900</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13670</v>
+        <v>13850</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+27.76%</t>
+          <t>'+29.44%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F3" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G3" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H3" t="n">
         <v>0.4</v>
@@ -702,7 +702,7 @@
         <v>0.42</v>
       </c>
       <c r="O3" t="n">
-        <v>175168035975</v>
+        <v>176123330405</v>
       </c>
       <c r="P3" t="n">
         <v>25700</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>삼성과 4381억 원 공급 계약 관련 언급. 역대급 거래량 발생 및 6G 통신 대장주로서의 가능성.</t>
+          <t>삼성과 4381억 공급 계약 재료 기반, 6G 통신 대장주로서의 강세 기대. 역대급 거래량 기록.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['공급 계약', '삼성', '6G 통신']</t>
+          <t>['6G통신', '공급계약', '거래량']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16230</v>
+        <v>16200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.78%</t>
+          <t>'+14.57%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.15</v>
       </c>
       <c r="E4" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="F4" t="n">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="G4" t="n">
-        <v>1812</v>
+        <v>1861</v>
       </c>
       <c r="H4" t="n">
         <v>1.95</v>
@@ -794,7 +794,7 @@
         <v>1.8</v>
       </c>
       <c r="O4" t="n">
-        <v>588448160555</v>
+        <v>594645274540</v>
       </c>
       <c r="P4" t="n">
         <v>31500</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>외국인/기관 600억 대량 순매수 및 미국 자회사 대규모 수주 기대. 16500원 돌파 및 10만 원 상승 전망.</t>
+          <t>외국인/기관 대량 순매수, 미국 자회사 대규모 광통신 수주 기대감. 16000원 지지선 확보 및 우상향 추세.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['외국인 순매수', '미국 자회사', '대규모 수주']</t>
+          <t>['광통신', '수주', '순매수']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4425</v>
+        <v>4430</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.40%</t>
+          <t>'+7.52%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.03</v>
       </c>
       <c r="E5" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F5" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G5" t="n">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="H5" t="n">
         <v>0.74</v>
@@ -886,7 +886,7 @@
         <v>0.77</v>
       </c>
       <c r="O5" t="n">
-        <v>309669222307</v>
+        <v>310928775627</v>
       </c>
       <c r="P5" t="n">
         <v>8100</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>광통신 관련 미장 상승 영향 및 젠슨 황 언급. 4천원 지지선 확보 후 추가 상승 기대.</t>
+          <t>광통신 관련 기대감과 함께 급등 가능성 언급. 4천원 지지선 확인, 운전 주체에 대한 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['광통신', '젠슨 황', '지지선']</t>
+          <t>['광통신', '급등']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4735</v>
+        <v>4690</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.22%</t>
+          <t>'+4.22%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.82</v>
       </c>
       <c r="E6" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F6" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G6" t="n">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="H6" t="n">
         <v>1.66</v>
@@ -978,7 +978,7 @@
         <v>0.84</v>
       </c>
       <c r="O6" t="n">
-        <v>122486628303</v>
+        <v>123464150327</v>
       </c>
       <c r="P6" t="n">
         <v>6190</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>삼성과 4381억 원 규모 공급 계약 체결. 잠재력 및 재료 보유 종목으로 10000원 직행 기대.</t>
+          <t>삼성과의 4381억 공급 계약 사실 기반, 높은 잠재력과 매집 정황 언급. 10000원 직행 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['공급 계약', '삼성', '잠재력']</t>
+          <t>['공급계약', '삼성', '매집']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>194300</v>
+        <v>193800</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+3.85%</t>
+          <t>'+3.58%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F7" t="n">
         <v>48</v>
       </c>
       <c r="G7" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H7" t="n">
         <v>75.66</v>
@@ -1070,7 +1070,7 @@
         <v>75.67</v>
       </c>
       <c r="O7" t="n">
-        <v>503831926650</v>
+        <v>513375240700</v>
       </c>
       <c r="P7" t="n">
         <v>243500</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7140</v>
+        <v>7100</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.48%</t>
+          <t>'+2.90%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.09</v>
       </c>
       <c r="E8" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F8" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G8" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H8" t="n">
         <v>0.79</v>
@@ -1162,7 +1162,7 @@
         <v>0.7</v>
       </c>
       <c r="O8" t="n">
-        <v>76165846855</v>
+        <v>76354806395</v>
       </c>
       <c r="P8" t="n">
         <v>10360</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1743000</v>
+        <v>1736000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.14%</t>
+          <t>'+2.72%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="G9" t="n">
-        <v>2004</v>
+        <v>2020</v>
       </c>
       <c r="H9" t="n">
         <v>50.2</v>
@@ -1254,7 +1254,7 @@
         <v>50.27</v>
       </c>
       <c r="O9" t="n">
-        <v>3110017203000</v>
+        <v>3183747645000</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>젠슨 황 관련 언급과 함께 외인 선물 매수세 유입. 자사주 매입 및 소각 기대감 속에 240만 원 목표.</t>
+          <t>외인 선물 대량 매수, 자사주 매입 및 소각 기대감. 실적 발표 시즌 도래.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['젠슨 황', '자사주 매입', '외인 선물']</t>
+          <t>['자사주매입', '외인선물']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>한국첨단소재</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3425</v>
+        <v>3585</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+1.93%</t>
+          <t>'+1.99%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-1.34</v>
+        <v>-0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>87</v>
+        <v>139</v>
       </c>
       <c r="F10" t="n">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="G10" t="n">
-        <v>189</v>
+        <v>540</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>3360</v>
+        <v>3515</v>
       </c>
       <c r="K10" t="n">
-        <v>3570</v>
+        <v>4120</v>
       </c>
       <c r="L10" t="n">
-        <v>3910</v>
+        <v>4140</v>
       </c>
       <c r="M10" t="n">
-        <v>3345</v>
+        <v>3555</v>
       </c>
       <c r="N10" t="n">
-        <v>1.34</v>
+        <v>3.16</v>
       </c>
       <c r="O10" t="n">
-        <v>101767807605</v>
+        <v>17954420970</v>
       </c>
       <c r="P10" t="n">
-        <v>5100</v>
+        <v>16110</v>
       </c>
       <c r="Q10" t="n">
-        <v>966</v>
+        <v>2300</v>
       </c>
       <c r="R10" t="n">
-        <v>-31000</v>
+        <v>-386000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-206000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>양자내성암호, 양자보안 관련 트럼프 행정명령 수혜 기대. 대한광통신과 유사한 흐름.</t>
+          <t>최대주주 유한양행 언급에도 불구하고, 사기 도박판 및 개미 모집 후 주가 하락에 대한 부정적인 전망 제시.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['양자암호', '보안', '트럼프']</t>
+          <t>['최대주주', '주가 하락', '공매도']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,77 +1384,77 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>062970</t>
+          <t>424870</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3580</v>
+        <v>252000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.85%</t>
+          <t>'+1.41%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>135</v>
+        <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>78</v>
+        <v>445</v>
       </c>
       <c r="G11" t="n">
-        <v>523</v>
+        <v>1519</v>
       </c>
       <c r="H11" t="n">
-        <v>3.11</v>
+        <v>46.56</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>3515</v>
+        <v>248500</v>
       </c>
       <c r="K11" t="n">
-        <v>4120</v>
+        <v>248000</v>
       </c>
       <c r="L11" t="n">
-        <v>4140</v>
+        <v>254000</v>
       </c>
       <c r="M11" t="n">
-        <v>3565</v>
+        <v>247500</v>
       </c>
       <c r="N11" t="n">
-        <v>3.16</v>
+        <v>46.57</v>
       </c>
       <c r="O11" t="n">
-        <v>17716983183</v>
+        <v>1899451452500</v>
       </c>
       <c r="P11" t="n">
-        <v>16110</v>
+        <v>374500</v>
       </c>
       <c r="Q11" t="n">
-        <v>2300</v>
+        <v>76700</v>
       </c>
       <c r="R11" t="n">
-        <v>-386000</v>
+        <v>-720000</v>
       </c>
       <c r="S11" t="n">
-        <v>-206000</v>
+        <v>754000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>최대주주가 유한양행이라는 언급이 있으나, 글쓴이는 사기 도박판이라 주장하며 투자 주의를 당부함. 공매도 및 개폭락 시작 가능성을 언급하며 반등 시 정리하라고 권고함.</t>
+          <t>총선 및 정치적 이슈 언급, 최고점 돌파 기대감 존재. 실질적인 근거 부족.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['최대주주', '공매도', '개폭락']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>107</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>424870</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>252500</v>
+        <v>13450</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+1.61%</t>
+          <t>'+1.13%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>58</v>
       </c>
       <c r="F12" t="n">
-        <v>450</v>
+        <v>43</v>
       </c>
       <c r="G12" t="n">
-        <v>1496</v>
+        <v>271</v>
       </c>
       <c r="H12" t="n">
-        <v>46.56</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,152 +1515,152 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>248500</v>
+        <v>13300</v>
       </c>
       <c r="K12" t="n">
-        <v>248000</v>
+        <v>13490</v>
       </c>
       <c r="L12" t="n">
-        <v>254000</v>
+        <v>13940</v>
       </c>
       <c r="M12" t="n">
-        <v>247500</v>
+        <v>13230</v>
       </c>
       <c r="N12" t="n">
-        <v>46.57</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1846632056250</v>
+        <v>16737325535</v>
       </c>
       <c r="P12" t="n">
-        <v>374500</v>
+        <v>19380</v>
       </c>
       <c r="Q12" t="n">
-        <v>76700</v>
+        <v>3200</v>
       </c>
       <c r="R12" t="n">
-        <v>-720000</v>
+        <v>-1000</v>
       </c>
       <c r="S12" t="n">
-        <v>754000</v>
+        <v>4000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정치적 이슈와 외부 요인 언급 속에 연말 최고점 돌파 기대. 외인 현물 순매수 전환 시 상승 전망.</t>
+          <t>주가 하락 및 부진한 흐름에 대한 불만 토로, 영양가 없는 호재 언급. 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['외인 순매수', '연말 전망', '정치 이슈']</t>
+          <t>['주가', '호재', '투자심리']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>107</v>
+        <v>54</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13500</v>
+        <v>3395</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+1.50%</t>
+          <t>'+1.04%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-1.34</v>
       </c>
       <c r="E13" t="n">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="F13" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="G13" t="n">
-        <v>263</v>
+        <v>192</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>13300</v>
+        <v>3360</v>
       </c>
       <c r="K13" t="n">
-        <v>13490</v>
+        <v>3570</v>
       </c>
       <c r="L13" t="n">
-        <v>13940</v>
+        <v>3910</v>
       </c>
       <c r="M13" t="n">
-        <v>13230</v>
+        <v>3345</v>
       </c>
       <c r="N13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="O13" t="n">
+        <v>102175342829</v>
+      </c>
+      <c r="P13" t="n">
+        <v>5100</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>966</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-31000</v>
+      </c>
+      <c r="S13" t="n">
         <v>0</v>
       </c>
-      <c r="O13" t="n">
-        <v>16506694435</v>
-      </c>
-      <c r="P13" t="n">
-        <v>19380</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3200</v>
-      </c>
-      <c r="R13" t="n">
-        <v>-1000</v>
-      </c>
-      <c r="S13" t="n">
-        <v>4000</v>
-      </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>주가 하락 및 부진한 흐름에 대한 불만 토로, 영양가 없는 호재 언급. 투자 심리 위축.</t>
+          <t>양자내성암호, 양자보안 관련 트럼프 행정명령 수혜 기대. 대한광통신과 유사한 흐름.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['주가', '호재', '투자심리']</t>
+          <t>['양자암호', '보안', '트럼프']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>062970</t>
         </is>
       </c>
     </row>
@@ -1682,13 +1682,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F14" t="n">
         <v>78</v>
       </c>
       <c r="G14" t="n">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="H14" t="n">
         <v>0.67</v>
@@ -1714,7 +1714,7 @@
         <v>0.6</v>
       </c>
       <c r="O14" t="n">
-        <v>115842697890</v>
+        <v>116375569905</v>
       </c>
       <c r="P14" t="n">
         <v>15960</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8500</v>
+        <v>8510</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.28%</t>
+          <t>'-1.16%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.5</v>
       </c>
       <c r="E15" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="F15" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G15" t="n">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="H15" t="n">
         <v>26.66</v>
@@ -1806,7 +1806,7 @@
         <v>27.16</v>
       </c>
       <c r="O15" t="n">
-        <v>11696941135</v>
+        <v>11845833790</v>
       </c>
       <c r="P15" t="n">
         <v>17950</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>경영진 성과급 논란 및 재무 구조 악화 우려. 삼성디스플레이와의 비교 속 주가 부진.</t>
+          <t>낮은 PBR 언급에도 불구, 삼성디스플레이와의 비교 및 재무 상태에 대한 우려. 외인 매도 지속.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['재무 구조', '경영진', '삼성디스플레이']</t>
+          <t>['PBR', '재무상태']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1851,83 +1851,83 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>한컴위드</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5145</v>
+        <v>10470</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.63%</t>
+          <t>'-1.78%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-1.39</v>
+        <v>1.29</v>
       </c>
       <c r="E16" t="n">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="F16" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="G16" t="n">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="H16" t="n">
-        <v>1.29</v>
+        <v>19.22</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>5230</v>
+        <v>10660</v>
       </c>
       <c r="K16" t="n">
-        <v>5750</v>
+        <v>10500</v>
       </c>
       <c r="L16" t="n">
-        <v>5880</v>
+        <v>10900</v>
       </c>
       <c r="M16" t="n">
-        <v>5020</v>
+        <v>10060</v>
       </c>
       <c r="N16" t="n">
-        <v>2.68</v>
+        <v>17.93</v>
       </c>
       <c r="O16" t="n">
-        <v>62659436545</v>
+        <v>117307581890</v>
       </c>
       <c r="P16" t="n">
-        <v>8980</v>
+        <v>22450</v>
       </c>
       <c r="Q16" t="n">
-        <v>2795</v>
+        <v>1760</v>
       </c>
       <c r="R16" t="n">
-        <v>98000</v>
+        <v>-475000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 사이버보안주 강세 속 양자보안 구축 의무화 및 3기업 독점 관련 기대.</t>
+          <t>연기금 순매수세 유입. 투주 물량 소화 중이나 주가 상승 모멘텀 불확실.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['양자보안', '사이버보안', '독점']</t>
+          <t>['연기금', '순매수', '투주']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,90 +1936,90 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>054920</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10460</v>
+        <v>31700</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.88%</t>
+          <t>'-2.31%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.29</v>
+        <v>-0.34</v>
       </c>
       <c r="E17" t="n">
-        <v>102</v>
+        <v>216</v>
       </c>
       <c r="F17" t="n">
-        <v>64</v>
+        <v>136</v>
       </c>
       <c r="G17" t="n">
-        <v>167</v>
+        <v>1141</v>
       </c>
       <c r="H17" t="n">
-        <v>19.22</v>
+        <v>17.16</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>10660</v>
+        <v>32450</v>
       </c>
       <c r="K17" t="n">
-        <v>10500</v>
+        <v>32850</v>
       </c>
       <c r="L17" t="n">
-        <v>10900</v>
+        <v>32850</v>
       </c>
       <c r="M17" t="n">
-        <v>10060</v>
+        <v>30900</v>
       </c>
       <c r="N17" t="n">
-        <v>17.93</v>
+        <v>17.5</v>
       </c>
       <c r="O17" t="n">
-        <v>116924229360</v>
+        <v>9032734000</v>
       </c>
       <c r="P17" t="n">
-        <v>22450</v>
+        <v>69200</v>
       </c>
       <c r="Q17" t="n">
-        <v>1760</v>
+        <v>24150</v>
       </c>
       <c r="R17" t="n">
-        <v>-475000</v>
+        <v>-83000</v>
       </c>
       <c r="S17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>연기금 순매수세 유입. 투주 물량 소화 중이나 주가 상승 모멘텀 불확실.</t>
+          <t>담관암, 간암 FDA 순차 승인 기대감 속, 유럽 신약 신청 시점에 대한 의구심 및 과거 실패 사례 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['연기금', '순매수', '투주']</t>
+          <t>['FDA', '신약', '담관암']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18740</v>
+        <v>20200</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.04%</t>
+          <t>'-2.42%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.11</v>
+        <v>-0.39</v>
       </c>
       <c r="E18" t="n">
-        <v>110</v>
+        <v>145</v>
       </c>
       <c r="F18" t="n">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="G18" t="n">
-        <v>404</v>
+        <v>354</v>
       </c>
       <c r="H18" t="n">
-        <v>10.64</v>
+        <v>28.51</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,51 +2067,51 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>19130</v>
+        <v>20700</v>
       </c>
       <c r="K18" t="n">
-        <v>19160</v>
+        <v>20750</v>
       </c>
       <c r="L18" t="n">
-        <v>19340</v>
+        <v>20750</v>
       </c>
       <c r="M18" t="n">
-        <v>18330</v>
+        <v>20200</v>
       </c>
       <c r="N18" t="n">
-        <v>10.53</v>
+        <v>28.9</v>
       </c>
       <c r="O18" t="n">
-        <v>51344890725</v>
+        <v>28242865050</v>
       </c>
       <c r="P18" t="n">
-        <v>40350</v>
+        <v>35350</v>
       </c>
       <c r="Q18" t="n">
-        <v>3320</v>
+        <v>18440</v>
       </c>
       <c r="R18" t="n">
-        <v>-116000</v>
+        <v>-677000</v>
       </c>
       <c r="S18" t="n">
-        <v>-90000</v>
+        <v>-51000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>대차해지 운동 독려하며 주가 조작 의혹 제기. 2만 원 돌파 및 10만 원 이상 상승 기대.</t>
+          <t>LNG선 수주 성공 및 IBK 목표주가 상향 제시. 정치적 이슈와 공매도에 대한 부정적 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['대차해지', '주가 조작', '대형 계약']</t>
+          <t>['LNG선', '수주']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,77 +2120,77 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>한컴위드</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20225</v>
+        <v>5100</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.29%</t>
+          <t>'-2.49%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.39</v>
+        <v>-1.39</v>
       </c>
       <c r="E19" t="n">
-        <v>136</v>
+        <v>86</v>
       </c>
       <c r="F19" t="n">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="G19" t="n">
-        <v>340</v>
+        <v>178</v>
       </c>
       <c r="H19" t="n">
-        <v>28.51</v>
+        <v>1.29</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>20700</v>
+        <v>5230</v>
       </c>
       <c r="K19" t="n">
-        <v>20750</v>
+        <v>5750</v>
       </c>
       <c r="L19" t="n">
-        <v>20750</v>
+        <v>5880</v>
       </c>
       <c r="M19" t="n">
-        <v>20200</v>
+        <v>5020</v>
       </c>
       <c r="N19" t="n">
-        <v>28.9</v>
+        <v>2.68</v>
       </c>
       <c r="O19" t="n">
-        <v>27518839175</v>
+        <v>62815540540</v>
       </c>
       <c r="P19" t="n">
-        <v>35350</v>
+        <v>8980</v>
       </c>
       <c r="Q19" t="n">
-        <v>18440</v>
+        <v>2795</v>
       </c>
       <c r="R19" t="n">
-        <v>-677000</v>
+        <v>98000</v>
       </c>
       <c r="S19" t="n">
-        <v>-51000</v>
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1.6조 원 규모 LNG선 수주 소식. IBK투자증권 목표주가 3만7000원 제시 및 매수 투자의견.</t>
+          <t>미국 사이버보안주 강세 속 양자보안 구축 의무화 및 3기업 독점 관련 기대.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['LNG선 수주', 'IBK 목표주가', '공매도']</t>
+          <t>['양자보안', '사이버보안', '독점']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,90 +2212,90 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>054920</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31600</v>
+        <v>83800</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-2.62%</t>
+          <t>'-2.78%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.34</v>
+        <v>-0.08</v>
       </c>
       <c r="E20" t="n">
-        <v>213</v>
+        <v>293</v>
       </c>
       <c r="F20" t="n">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="G20" t="n">
-        <v>1137</v>
+        <v>935</v>
       </c>
       <c r="H20" t="n">
-        <v>17.16</v>
+        <v>23.37</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>32450</v>
+        <v>86200</v>
       </c>
       <c r="K20" t="n">
-        <v>32850</v>
+        <v>86200</v>
       </c>
       <c r="L20" t="n">
-        <v>32850</v>
+        <v>86300</v>
       </c>
       <c r="M20" t="n">
-        <v>30900</v>
+        <v>83500</v>
       </c>
       <c r="N20" t="n">
-        <v>17.5</v>
+        <v>23.45</v>
       </c>
       <c r="O20" t="n">
-        <v>8794752900</v>
+        <v>133038937050</v>
       </c>
       <c r="P20" t="n">
-        <v>69200</v>
+        <v>139200</v>
       </c>
       <c r="Q20" t="n">
-        <v>24150</v>
+        <v>57000</v>
       </c>
       <c r="R20" t="n">
-        <v>-83000</v>
+        <v>-102000</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-86000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>담관암, 간암 FDA 순차 승인 기대감 속, 유럽 신약 신청 시점에 대한 의구심 및 과거 실패 사례 언급.</t>
+          <t>웨스팅하우스 지분 인수 관련 기대감과 공매도 세력의 움직임 혼재. 대미 투자 연기 단독 뉴스.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['FDA', '신약', '담관암']</t>
+          <t>['웨스팅하우스', '공매도']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,38 +2304,38 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>83800</v>
+        <v>18590</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-2.78%</t>
+          <t>'-2.82%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.08</v>
+        <v>0.11</v>
       </c>
       <c r="E21" t="n">
-        <v>283</v>
+        <v>112</v>
       </c>
       <c r="F21" t="n">
-        <v>153</v>
+        <v>64</v>
       </c>
       <c r="G21" t="n">
-        <v>888</v>
+        <v>408</v>
       </c>
       <c r="H21" t="n">
-        <v>23.37</v>
+        <v>10.64</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,51 +2343,51 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>86200</v>
+        <v>19130</v>
       </c>
       <c r="K21" t="n">
-        <v>86200</v>
+        <v>19160</v>
       </c>
       <c r="L21" t="n">
-        <v>86300</v>
+        <v>19340</v>
       </c>
       <c r="M21" t="n">
-        <v>83500</v>
+        <v>18330</v>
       </c>
       <c r="N21" t="n">
-        <v>23.45</v>
+        <v>10.53</v>
       </c>
       <c r="O21" t="n">
-        <v>129553893550</v>
+        <v>52647102195</v>
       </c>
       <c r="P21" t="n">
-        <v>139200</v>
+        <v>40350</v>
       </c>
       <c r="Q21" t="n">
-        <v>57000</v>
+        <v>3320</v>
       </c>
       <c r="R21" t="n">
-        <v>-102000</v>
+        <v>-116000</v>
       </c>
       <c r="S21" t="n">
-        <v>-86000</v>
+        <v>-90000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>웨스팅하우스 지분 인수 및 경영권 참여 가능성 언급. 공매도 세력과의 갈등 및 대미 투자 연기 이슈.</t>
+          <t>대차해지 운동 독려하며 주가 조작 의혹 제기. 2만 원 돌파 및 10만 원 이상 상승 기대.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['웨스팅하우스', '공매도', '대미 투자']</t>
+          <t>['대차해지', '주가 조작', '대형 계약']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17000</v>
+        <v>16950</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-3.13%</t>
+          <t>'-3.42%</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2424,7 +2424,7 @@
         <v>92</v>
       </c>
       <c r="G22" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="H22" t="n">
         <v>0.45</v>
@@ -2450,7 +2450,7 @@
         <v>0.35</v>
       </c>
       <c r="O22" t="n">
-        <v>158297933885</v>
+        <v>158545859745</v>
       </c>
       <c r="P22" t="n">
         <v>30550</v>
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5920</v>
+        <v>5940</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-6.18%</t>
+          <t>'-5.86%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>-2.04</v>
       </c>
       <c r="E23" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F23" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G23" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="H23" t="n">
         <v>0.98</v>
@@ -2542,7 +2542,7 @@
         <v>3.02</v>
       </c>
       <c r="O23" t="n">
-        <v>42199592825</v>
+        <v>42463470765</v>
       </c>
       <c r="P23" t="n">
         <v>11370</v>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>14020</v>
+        <v>14010</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-6.41%</t>
+          <t>'-6.48%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="F24" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G24" t="n">
-        <v>598</v>
+        <v>609</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -2634,7 +2634,7 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>33493899300</v>
+        <v>33756726420</v>
       </c>
       <c r="P24" t="n">
         <v>36200</v>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>국제유가 상승 및 미국 에너지주 폭등에 따른 기대감. 그러나 비축유 이슈 및 FOMC 대비 경계감 존재.</t>
+          <t>국제유가 상승 및 에너지주 폭등 기대감에도 불구하고, 국내장 하락 및 비축유 문제 등 하락 요인 언급. FOMC 대비.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
